--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>2490.846435546875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2522.320068359375</v>
+      </c>
+      <c r="H56" t="n">
+        <v>31.4736328125</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.247804876443448</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.07808106120905</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:03</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2516.554443359375</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>2511.205322,2509.528564,2508.287354,2507.708008,2507.758789,2506.948730,2505.855957,2503.460938,2502.809082,2501.979980,2500.980713,2500.898438,2498.820801,2497.524170,2496.728516,2494.369141,2494.117188,2492.467041,2491.899658,2491.181396,2491.604980,2490.705078,2490.104736,2490.846436</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2511.459961,2519.050049,2523.629883,2533.050049,2530.540039,2533.090088,2536.090088,2535.219971,2543.969971,2539.100098,2534.510010,2531.340088,2525.350098,2522.010010,2518.919922,2520.040039,2523.360107,2522.639893,2525.350098,2524.419922,2525.239990,2521.090088,2520.159912,2522.320068</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.254639,9.521485,15.342529,25.342041,22.781250,26.141358,30.234131,31.759033,41.160889,37.120118,33.529297,30.441650,26.529297,24.485840,22.191406,25.670898,29.242919,30.172852,33.450440,33.238526,33.635010,30.385010,30.055176,31.473632</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.010139,0.377979,0.607955,1.000456,0.900253,1.031995,1.192155,1.252713,1.617979,1.461940,1.322910,1.202590,1.050520,0.970886,0.880989,1.018670,1.158888,1.196082,1.324586,1.316680,1.331953,1.205233,1.192590,1.247805</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1.07808106120905</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>2510.087158,2508.637939,2508.242676,2506.195312,2507.093262,2505.547119,2499.458252,2499.779053,2497.089355,2499.552979,2497.160156,2494.262695,2489.469727,2492.969238,2490.762207,2489.160156,2487.483887,2485.916992,2483.254639,2480.257812,2484.547363,2484.175781,2483.177979,2484.202637</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>2506.665283,2502.338867,2500.887451,2498.666016,2496.673096,2492.830078,2489.661865,2486.291504,2484.500488,2481.604004,2478.656006,2477.873535,2476.345947,2472.798340,2473.396484,2469.073975,2466.346680,2464.590332,2462.234619,2462.221191,2462.879883,2458.699219,2457.694824,2456.783691</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:03</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2521.988770,2522.324951,2521.833008,2523.603027,2522.041748,2522.394287,2522.470703,2521.612549,2522.112549,2522.769531,2521.676758,2521.061768,2520.596436,2518.923340,2519.228027,2518.325928,2518.571533,2518.449707,2517.902588,2519.122559,2517.571289,2517.947754,2517.985596,2516.554443</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2520.434814,2517.161133,2523.591797,2522.833008,2524.481689,2521.047363,2518.184082,2517.126709,2513.915527,2519.399414,2517.478027,2514.843750,2513.898926,2517.421875,2511.617676,2511.326660,2513.896729,2511.366211,2511.425781,2511.044434,2511.014648,2507.526855,2509.138428,2512.662598</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2512.052490,2512.974609,2507.684570,2507.271729,2503.955078,2500.910645,2497.437012,2492.320557,2492.281006,2490.799072,2486.989746,2482.100098,2480.822510,2477.650635,2474.519775,2472.575439,2472.197266,2471.781494,2464.453369,2463.710693,2461.396973,2461.094238,2460.572754,2456.757812</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2517.066406,2515.970947,2513.563232,2514.921875,2511.283447,2509.625977,2508.738281,2505.664551,2506.751709,2505.797852,2502.218994,2500.601318,2500.061523,2495.390625,2494.620850,2493.845947,2492.391357,2493.310059,2491.388916,2491.419434,2488.681396,2487.780029,2486.160156,2485.398438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>2516.554443359375</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2512.81005859375</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.744384765625</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.1490118504110286</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9501454683192322</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2502.40673828125</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>2521.988770,2522.324951,2521.833008,2523.603027,2522.041748,2522.394287,2522.470703,2521.612549,2522.112549,2522.769531,2521.676758,2521.061768,2520.596436,2518.923340,2519.228027,2518.325928,2518.571533,2518.449707,2517.902588,2519.122559,2517.571289,2517.947754,2517.985596,2516.554443</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2522.020020,2512.370117,2517.020020,2493.330078,2484.270020,2471.030029,2480.790039,2476.590088,2478.370117,2491.929932,2490.199951,2504.000000,2504.100098,2508.500000,2505.219971,2511.939941,2507.820068,2474.570068,2475.879883,2483.129883,2492.199951,2510.310059,2511.760010,2512.810059</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.031250,9.954834,4.812988,30.272949,37.771728,51.364258,41.680664,45.022461,43.742432,30.839599,31.476807,17.061768,16.496338,10.423340,14.008056,6.385987,10.751465,43.879639,42.022705,35.992676,25.371338,7.637695,6.225586,3.744384</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.001239,0.396233,0.191218,1.214157,1.520436,2.078658,1.680137,1.817921,1.764968,1.237579,1.264027,0.681381,0.658773,0.415521,0.559155,0.254225,0.428718,1.773223,1.697284,1.449488,1.018030,0.304253,0.247858,0.149012</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9501454683192322</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>2520.434814,2517.161133,2523.591797,2522.833008,2524.481689,2521.047363,2518.184082,2517.126709,2513.915527,2519.399414,2517.478027,2514.843750,2513.898926,2517.421875,2511.617676,2511.326660,2513.896729,2511.366211,2511.425781,2511.044434,2511.014648,2507.526855,2509.138428,2512.662598</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>2517.066406,2515.970947,2513.563232,2514.921875,2511.283447,2509.625977,2508.738281,2505.664551,2506.751709,2505.797852,2502.218994,2500.601318,2500.061523,2495.390625,2494.620850,2493.845947,2492.391357,2493.310059,2491.388916,2491.419434,2488.681396,2487.780029,2486.160156,2485.398438</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2510.049316,2511.218994,2510.301025,2511.409912,2509.794189,2509.792969,2509.417480,2509.214111,2509.075195,2508.761719,2508.218750,2508.900391,2508.374756,2507.813232,2507.838623,2508.195312,2506.208008,2504.830811,2504.246582,2505.541016,2504.125244,2503.908936,2503.041504,2502.406738</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2509.728027,2509.474365,2511.145996,2510.396729,2511.224121,2509.106445,2509.038086,2507.177734,2506.485352,2510.661621,2507.738770,2504.264160,2505.776855,2510.770752,2505.021973,2503.683594,2505.308105,2503.976318,2504.591309,2500.968018,2500.055664,2497.954590,2502.248779,2501.081543</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2498.548828,2498.447754,2493.294922,2492.952637,2488.427246,2486.157227,2484.200195,2479.022705,2479.393311,2476.228271,2474.929688,2472.051758,2469.237793,2468.662354,2467.842773,2466.581543,2464.471191,2463.572021,2456.419922,2456.352295,2457.234375,2456.307129,2454.966553,2453.321777</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2503.715820,2502.879395,2499.446777,2499.948242,2496.821289,2494.569580,2494.198486,2491.656738,2491.813232,2489.872070,2486.932129,2488.433105,2486.373047,2483.737549,2484.098145,2484.121826,2481.064697,2480.109131,2477.692871,2479.188965,2477.387695,2476.190186,2474.311768,2473.964355</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>2502.40673828125</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2489.860107421875</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12.546630859375</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.503909067902068</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.5945679304175002</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:51</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2496.260986328125</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>2510.049316,2511.218994,2510.301025,2511.409912,2509.794189,2509.792969,2509.417480,2509.214111,2509.075195,2508.761719,2508.218750,2508.900391,2508.374756,2507.813232,2507.838623,2508.195312,2506.208008,2504.830811,2504.246582,2505.541016,2504.125244,2503.908936,2503.041504,2502.406738</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2515.489990,2513.370117,2521.750000,2517.500000,2522.909912,2512.000000,2508.060059,2504.189941,2499.169922,2500.600098,2507.570068,2528.620117,2533.429932,2539.050049,2539.520020,2570.449951,2546.530029,2532.870117,2515.780029,2515.649902,2515.030029,2511.709961,2498.209961,2489.860107</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>5.440674,2.151123,11.448975,6.090088,13.115723,2.207031,1.357421,5.024170,9.905273,8.161621,0.648682,19.719726,25.055176,31.236817,31.681397,62.254639,40.322021,28.039306,11.533447,10.108886,10.904785,7.801025,4.831543,12.546631</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.216287,0.085587,0.454009,0.241910,0.519865,0.087860,0.054122,0.200631,0.396343,0.326387,0.025869,0.779861,0.988982,1.230256,1.247535,2.421935,1.583410,1.107017,0.458444,0.401840,0.433585,0.310586,0.193400,0.503909</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.5945679304175002</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>2509.728027,2509.474365,2511.145996,2510.396729,2511.224121,2509.106445,2509.038086,2507.177734,2506.485352,2510.661621,2507.738770,2504.264160,2505.776855,2510.770752,2505.021973,2503.683594,2505.308105,2503.976318,2504.591309,2500.968018,2500.055664,2497.954590,2502.248779,2501.081543</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>2503.715820,2502.879395,2499.446777,2499.948242,2496.821289,2494.569580,2494.198486,2491.656738,2491.813232,2489.872070,2486.932129,2488.433105,2486.373047,2483.737549,2484.098145,2484.121826,2481.064697,2480.109131,2477.692871,2479.188965,2477.387695,2476.190186,2474.311768,2473.964355</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:51</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2491.247070,2491.409180,2491.991943,2492.553223,2492.966797,2492.839111,2492.947510,2494.014160,2493.650879,2493.928711,2495.514648,2495.537598,2496.870605,2496.371094,2498.323730,2498.062012,2498.229492,2497.538574,2497.612061,2498.336914,2496.389160,2496.953125,2496.596680,2496.260986</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2492.008301,2491.260010,2492.261230,2492.670410,2494.590088,2494.307129,2491.524902,2489.823730,2491.182861,2494.418457,2494.945557,2491.644775,2490.955566,2497.723633,2495.729248,2495.977539,2496.109863,2493.020752,2494.129395,2493.022461,2491.771973,2490.212402,2493.944824,2492.373047</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2480.277344,2478.520752,2474.038574,2471.685547,2469.331299,2467.594727,2466.115967,2462.692627,2463.057617,2460.571777,2462.927979,2459.153809,2458.559570,2457.757080,2459.270996,2456.319092,2455.675293,2455.145508,2449.946289,2449.103027,2448.310059,2448.112793,2447.442139,2445.979980</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2484.833740,2482.362305,2480.302734,2479.480713,2478.478516,2477.205811,2478.317627,2476.148438,2476.884277,2473.513184,2474.634521,2476.233398,2475.633057,2472.607178,2476.304443,2474.240967,2473.444336,2472.999268,2472.124512,2471.928955,2469.602051,2469.659424,2468.324219,2466.629883</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>2496.260986328125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2401.219970703125</v>
+      </c>
+      <c r="H59" t="n">
+        <v>95.041015625</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.958030367254113</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.629821365578735</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:06</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2416.45263671875</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>2491.247070,2491.409180,2491.991943,2492.553223,2492.966797,2492.839111,2492.947510,2494.014160,2493.650879,2493.928711,2495.514648,2495.537598,2496.870605,2496.371094,2498.323730,2498.062012,2498.229492,2497.538574,2497.612061,2498.336914,2496.389160,2496.953125,2496.596680,2496.260986</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2495.969971,2485.520020,2473.090088,2476.229980,2473.429932,2482.669922,2475.350098,2478.709961,2452.320068,2405.409912,2423.199951,2420.879883,2439.610107,2401.260010,2414.330078,2405.860107,2390.169922,2395.159912,2396.139893,2397.739990,2389.090088,2401.159912,2400.090088,2401.219971</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>4.722901,5.889160,18.901855,16.323243,19.536865,10.169189,17.597412,15.304199,41.330811,88.518799,72.314697,74.657715,57.260498,95.111084,83.993652,92.201905,108.059570,102.378662,101.472168,100.596924,107.299072,95.793213,96.506592,95.041015</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.189221,0.236939,0.764301,0.659197,0.789869,0.409607,0.710906,0.617426,1.685376,3.679988,2.984265,3.083908,2.347117,3.960882,3.478963,3.832388,4.520999,4.274398,4.234818,4.195489,4.491211,3.989456,4.020957,3.958030</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2.629821365578735</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>2492.008301,2491.260010,2492.261230,2492.670410,2494.590088,2494.307129,2491.524902,2489.823730,2491.182861,2494.418457,2494.945557,2491.644775,2490.955566,2497.723633,2495.729248,2495.977539,2496.109863,2493.020752,2494.129395,2493.022461,2491.771973,2490.212402,2493.944824,2492.373047</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>2484.833740,2482.362305,2480.302734,2479.480713,2478.478516,2477.205811,2478.317627,2476.148438,2476.884277,2473.513184,2474.634521,2476.233398,2475.633057,2472.607178,2476.304443,2474.240967,2473.444336,2472.999268,2472.124512,2471.928955,2469.602051,2469.659424,2468.324219,2466.629883</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:06</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2401.439941,2401.914062,2402.350830,2402.155029,2403.454102,2403.501709,2405.520996,2405.242188,2404.925781,2405.285645,2406.709717,2407.385742,2410.122070,2410.499512,2412.880127,2413.156250,2413.565430,2414.158936,2415.373535,2415.408203,2416.062744,2416.966309,2416.888916,2416.452637</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2405.592529,2402.131348,2402.037598,2405.212646,2407.257812,2407.658203,2409.384766,2404.060303,2408.912354,2408.350830,2407.230469,2409.232910,2410.187012,2414.420898,2415.435791,2406.668213,2415.896240,2418.153320,2418.071777,2415.357666,2417.158691,2413.588623,2417.994141,2416.338379</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2385.710938,2381.723389,2375.172363,2370.428223,2368.283936,2364.848877,2366.741699,2359.831055,2358.184082,2356.316162,2356.474609,2353.789551,2354.069092,2350.877686,2354.034668,2350.916504,2349.041016,2348.336914,2343.796143,2340.944092,2342.050049,2341.271240,2340.670898,2338.853760</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2391.672363,2388.251709,2384.701172,2381.475098,2380.530273,2379.665527,2382.330078,2378.798828,2378.036621,2375.900391,2374.748535,2378.956543,2377.281982,2374.662354,2379.324707,2377.666016,2374.488770,2373.553711,2373.685547,2372.845703,2372.009033,2371.870605,2371.895508,2369.401855</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>2416.45263671875</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2429.2099609375</v>
+      </c>
+      <c r="H60" t="n">
+        <v>12.75732421875</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.5251635068146432</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.3967692100556841</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2435.15576171875</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>2401.439941,2401.914062,2402.350830,2402.155029,2403.454102,2403.501709,2405.520996,2405.242188,2404.925781,2405.285645,2406.709717,2407.385742,2410.122070,2410.499512,2412.880127,2413.156250,2413.565430,2414.158936,2415.373535,2415.408203,2416.062744,2416.966309,2416.888916,2416.452637</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2405.330078,2404.729980,2394.760010,2400.770020,2403.899902,2403.000000,2420.760010,2404.760010,2392.169922,2387.540039,2391.290039,2389.989990,2387.199951,2395.540039,2407.389893,2408.580078,2402.860107,2390.699951,2416.449951,2416.600098,2425.560059,2426.959961,2433.409912,2429.209961</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>3.890137,2.815918,7.590820,1.385009,0.445800,0.501709,15.239014,0.482178,12.755859,17.745606,15.419678,17.395752,22.922119,14.959473,5.490234,4.576172,10.705323,23.458985,1.076416,1.191895,9.497315,9.993652,16.520996,12.757324</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.161730,0.117099,0.316976,0.057690,0.018545,0.020878,0.629514,0.020051,0.533234,0.743259,0.644827,0.727859,0.960209,0.624472,0.228058,0.189995,0.445524,0.981260,0.044545,0.049321,0.391551,0.411777,0.678924,0.525163</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.3967692100556841</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>2405.592529,2402.131348,2402.037598,2405.212646,2407.257812,2407.658203,2409.384766,2404.060303,2408.912354,2408.350830,2407.230469,2409.232910,2410.187012,2414.420898,2415.435791,2406.668213,2415.896240,2418.153320,2418.071777,2415.357666,2417.158691,2413.588623,2417.994141,2416.338379</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>2391.672363,2388.251709,2384.701172,2381.475098,2380.530273,2379.665527,2382.330078,2378.798828,2378.036621,2375.900391,2374.748535,2378.956543,2377.281982,2374.662354,2379.324707,2377.666016,2374.488770,2373.553711,2373.685547,2372.845703,2372.009033,2371.870605,2371.895508,2369.401855</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2429.395996,2430.550781,2430.937744,2430.255859,2431.943848,2432.413818,2433.358398,2433.365967,2432.038818,2433.538330,2433.838867,2434.548828,2434.725586,2434.920654,2434.001465,2434.251709,2433.825928,2433.997314,2434.338867,2434.644043,2435.009277,2435.013184,2435.125732,2435.155762</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2429.434570,2430.837891,2431.809082,2432.101318,2434.357910,2432.986816,2435.146729,2432.626953,2434.118896,2436.158691,2433.940674,2434.683838,2437.721924,2435.760742,2435.004883,2433.875732,2434.654297,2435.698730,2438.285156,2433.633545,2434.463623,2432.374268,2435.031738,2434.889160</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2417.359375,2414.108398,2408.481934,2403.170898,2402.654297,2400.215820,2398.896484,2394.946777,2392.339355,2389.687988,2388.389404,2384.817627,2385.090820,2383.210205,2381.765869,2379.137939,2377.174805,2374.830811,2370.360840,2367.160645,2368.056885,2365.773926,2365.546631,2363.897705</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2422.357178,2420.052979,2417.719238,2413.991699,2413.656250,2412.581055,2413.510742,2411.411377,2410.320801,2407.446777,2405.325928,2406.756836,2406.573486,2404.421875,2404.137939,2403.759766,2401.811523,2398.434082,2398.784180,2397.113037,2396.568115,2394.813477,2395.101318,2395.294434</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>2435.15576171875</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2471.52001953125</v>
+      </c>
+      <c r="H61" t="n">
+        <v>36.3642578125</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.471331711866808</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.7359847267492454</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:46</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2473.984619140625</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>2429.395996,2430.550781,2430.937744,2430.255859,2431.943848,2432.413818,2433.358398,2433.365967,2432.038818,2433.538330,2433.838867,2434.548828,2434.725586,2434.920654,2434.001465,2434.251709,2433.825928,2433.997314,2434.338867,2434.644043,2435.009277,2435.013184,2435.125732,2435.155762</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2434.719971,2438.919922,2442.050049,2443.229980,2436.600098,2433.419922,2440.199951,2457.639893,2460.060059,2458.800049,2467.989990,2468.229980,2460.669922,2449.760010,2447.340088,2451.439941,2445.429932,2443.870117,2445.439941,2445.870117,2454.899902,2460.439941,2476.929932,2471.520020</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>5.323975,8.369141,11.112305,12.974121,4.656250,1.006104,6.841553,24.273926,28.021241,25.261719,34.151123,33.681152,25.944336,14.839356,13.338623,17.188232,11.604004,9.872803,11.101074,11.226074,19.890625,25.426757,41.804200,36.364258</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.218669,0.343149,0.455040,0.531023,0.191096,0.041345,0.280369,0.987693,1.139047,1.027400,1.383763,1.364587,1.054361,0.605747,0.545025,0.701148,0.474518,0.403982,0.453950,0.458981,0.810242,1.033423,1.687743,1.471332</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.7359847267492454</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>2429.434570,2430.837891,2431.809082,2432.101318,2434.357910,2432.986816,2435.146729,2432.626953,2434.118896,2436.158691,2433.940674,2434.683838,2437.721924,2435.760742,2435.004883,2433.875732,2434.654297,2435.698730,2438.285156,2433.633545,2434.463623,2432.374268,2435.031738,2434.889160</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>2422.357178,2420.052979,2417.719238,2413.991699,2413.656250,2412.581055,2413.510742,2411.411377,2410.320801,2407.446777,2405.325928,2406.756836,2406.573486,2404.421875,2404.137939,2403.759766,2401.811523,2398.434082,2398.784180,2397.113037,2396.568115,2394.813477,2395.101318,2395.294434</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:46</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2469.888184,2469.952637,2469.168457,2468.920898,2468.738525,2468.378174,2468.085938,2469.479004,2469.256592,2470.079590,2469.986816,2470.235596,2469.293945,2469.195801,2468.959473,2469.223145,2469.991699,2469.556641,2470.380859,2471.057617,2471.931641,2473.121582,2473.625244,2473.984619</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2469.178223,2469.083496,2469.345215,2468.973633,2468.968750,2468.654541,2468.166016,2468.563965,2467.379150,2470.156006,2468.503906,2468.165527,2469.066650,2468.344238,2468.225098,2468.938232,2469.071045,2469.900146,2470.022949,2469.553955,2471.062988,2471.675781,2471.806641,2472.478516</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2459.593994,2456.375488,2451.131348,2448.001953,2445.533691,2442.268555,2439.913086,2439.074219,2436.887939,2434.661621,2432.781494,2430.922852,2430.420166,2428.333496,2427.165527,2425.229980,2425.106934,2422.976807,2420.714111,2419.491699,2418.921631,2419.503174,2419.740967,2419.078613</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2464.261230,2461.623535,2457.944580,2456.367676,2454.186768,2452.489746,2451.632812,2451.007324,2450.164062,2448.530273,2446.622314,2446.923584,2445.361084,2444.578613,2444.239990,2443.928223,2443.811768,2441.426758,2441.775635,2441.478271,2441.045410,2440.730469,2442.341797,2442.281982</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>2473.984619140625</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2621.659912109375</v>
+      </c>
+      <c r="H62" t="n">
+        <v>147.67529296875</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5.63289282056158</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.930915272479468</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:40</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2583.099853515625</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>2469.888184,2469.952637,2469.168457,2468.920898,2468.738525,2468.378174,2468.085938,2469.479004,2469.256592,2470.079590,2469.986816,2470.235596,2469.293945,2469.195801,2468.959473,2469.223145,2469.991699,2469.556641,2470.380859,2471.057617,2471.931641,2473.121582,2473.625244,2473.984619</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2478.370117,2484.919922,2487.600098,2503.159912,2505.830078,2511.350098,2505.800049,2500.159912,2552.790039,2581.590088,2583.219971,2596.489990,2606.780029,2611.669922,2636.800049,2631.540039,2626.310059,2619.689941,2611.340088,2626.199951,2612.469971,2622.639893,2619.330078,2621.659912</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>8.481933,14.967285,18.431641,34.239014,37.091553,42.971924,37.714111,30.680908,83.533447,111.510498,113.233155,126.254394,137.486084,142.474121,167.840576,162.316894,156.318360,150.133300,140.959229,155.142334,140.538330,149.518311,145.704834,147.675293</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.342238,0.602325,0.740941,1.367832,1.480210,1.711108,1.505073,1.227158,3.272241,4.319450,4.383411,4.862503,5.274173,5.455288,6.365313,6.168133,5.952015,5.730957,5.397965,5.907484,5.379519,5.701061,5.562676,5.632893</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>3.930915272479468</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>2469.178223,2469.083496,2469.345215,2468.973633,2468.968750,2468.654541,2468.166016,2468.563965,2467.379150,2470.156006,2468.503906,2468.165527,2469.066650,2468.344238,2468.225098,2468.938232,2469.071045,2469.900146,2470.022949,2469.553955,2471.062988,2471.675781,2471.806641,2472.478516</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>2464.261230,2461.623535,2457.944580,2456.367676,2454.186768,2452.489746,2451.632812,2451.007324,2450.164062,2448.530273,2446.622314,2446.923584,2445.361084,2444.578613,2444.239990,2443.928223,2443.811768,2441.426758,2441.775635,2441.478271,2441.045410,2440.730469,2442.341797,2442.281982</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:40</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2621.788330,2619.533936,2618.320068,2615.934570,2612.218262,2610.244629,2609.354980,2607.319824,2607.148682,2605.543945,2603.054199,2602.737305,2599.428467,2597.320557,2597.494141,2595.344971,2593.382812,2591.207275,2589.455811,2586.117676,2586.060547,2584.601562,2582.972412,2583.099854</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2618.581055,2614.695312,2615.522461,2613.085693,2607.238525,2604.723633,2600.089355,2602.426025,2599.039795,2598.654053,2594.488770,2592.448242,2588.615479,2589.976562,2587.682129,2589.630127,2581.916504,2582.282227,2578.684082,2577.682861,2575.068359,2579.625732,2574.535400,2572.526123</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2603.573486,2594.865234,2586.073486,2577.081299,2568.422607,2561.534424,2555.459473,2550.397461,2548.789551,2544.996582,2539.500244,2538.116211,2537.189453,2530.906250,2526.914551,2524.264404,2519.569824,2517.091309,2510.919922,2503.031006,2502.858887,2500.828613,2497.308594,2498.747314</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2612.803711,2606.265381,2599.286621,2594.955811,2586.327637,2581.835938,2579.301758,2574.099121,2573.352051,2570.651855,2566.391602,2566.625977,2561.190674,2558.141602,2555.919922,2554.628418,2550.019775,2547.742676,2543.974609,2539.064941,2538.223389,2534.279297,2533.493164,2533.694336</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>2583.099853515625</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2584.780029296875</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.68017578125</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.06500266027306974</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.084912521282875</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:42</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2560.0078125</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>2621.788330,2619.533936,2618.320068,2615.934570,2612.218262,2610.244629,2609.354980,2607.319824,2607.148682,2605.543945,2603.054199,2602.737305,2599.428467,2597.320557,2597.494141,2595.344971,2593.382812,2591.207275,2589.455811,2586.117676,2586.060547,2584.601562,2582.972412,2583.099854</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2628.090088,2626.389893,2626.010010,2644.399902,2640.189941,2637.260010,2638.590088,2641.550049,2637.629883,2638.280029,2640.590088,2649.870117,2644.929932,2638.399902,2634.330078,2635.379883,2627.560059,2630.110107,2633.639893,2626.729980,2618.389893,2573.719971,2587.179932,2584.780029</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6.301758,6.855957,7.689942,28.465332,27.971679,27.015381,29.235108,34.230225,30.481201,32.736084,37.535889,47.132812,45.501465,41.079345,36.835937,40.034912,34.177247,38.902832,44.184082,40.612304,32.329346,10.881591,4.207520,1.680175</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.239785,0.261041,0.292837,1.076438,1.059457,1.024373,1.107982,1.295839,1.155628,1.240812,1.421496,1.778684,1.720328,1.556979,1.398304,1.519132,1.300722,1.479133,1.677681,1.546116,1.234703,0.422796,0.162630,0.065003</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1.084912521282875</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>2618.581055,2614.695312,2615.522461,2613.085693,2607.238525,2604.723633,2600.089355,2602.426025,2599.039795,2598.654053,2594.488770,2592.448242,2588.615479,2589.976562,2587.682129,2589.630127,2581.916504,2582.282227,2578.684082,2577.682861,2575.068359,2579.625732,2574.535400,2572.526123</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>2612.803711,2606.265381,2599.286621,2594.955811,2586.327637,2581.835938,2579.301758,2574.099121,2573.352051,2570.651855,2566.391602,2566.625977,2561.190674,2558.141602,2555.919922,2554.628418,2550.019775,2547.742676,2543.974609,2539.064941,2538.223389,2534.279297,2533.493164,2533.694336</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:42</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2586.124023,2583.949219,2583.806641,2582.119141,2580.616211,2578.915527,2578.689941,2576.184326,2576.147705,2575.056641,2573.473145,2572.239258,2571.652832,2569.728760,2570.584229,2570.158203,2568.370850,2566.905762,2565.330811,2563.978271,2563.033203,2561.805664,2560.942139,2560.007812</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2584.937012,2582.305664,2582.281006,2579.533203,2577.585938,2574.342285,2572.844482,2570.656738,2572.088867,2569.591309,2567.844482,2566.470215,2564.636963,2563.531250,2563.921143,2563.952393,2561.977051,2560.764160,2558.833984,2558.158936,2557.426758,2554.593018,2555.020264,2554.995117</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2569.384766,2562.405518,2556.029297,2548.982422,2543.198730,2536.976074,2532.510498,2527.214111,2526.322998,2523.195312,2518.443848,2516.269531,2516.081543,2510.265381,2507.135742,2505.049316,2501.670410,2498.611816,2491.454590,2487.351074,2485.867920,2482.867920,2480.924561,2479.876465</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2577.472168,2572.412354,2566.924072,2563.412109,2558.150146,2554.154053,2552.620361,2547.495605,2546.590088,2544.607422,2541.027588,2539.863281,2536.902100,2533.806152,2531.955566,2531.709717,2527.728271,2525.877930,2521.580322,2519.687744,2517.528564,2514.007812,2513.112793,2511.974609</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>2560.0078125</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2659.580078125</v>
+      </c>
+      <c r="H64" t="n">
+        <v>99.572265625</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3.743909290191341</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.788327892924973</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:40</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2641.998046875</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>2586.124023,2583.949219,2583.806641,2582.119141,2580.616211,2578.915527,2578.689941,2576.184326,2576.147705,2575.056641,2573.473145,2572.239258,2571.652832,2569.728760,2570.584229,2570.158203,2568.370850,2566.905762,2565.330811,2563.978271,2563.033203,2561.805664,2560.942139,2560.007812</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2577.159912,2573.260010,2576.040039,2573.879883,2578.800049,2570.489990,2577.870117,2579.399902,2580.010010,2584.879883,2612.479980,2640.300049,2626.260010,2625.620117,2632.969971,2634.219971,2630.179932,2638.949951,2644.090088,2689.179932,2649.590088,2661.139893,2665.219971,2659.580078</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>8.964111,10.689209,7.766602,8.239258,1.816162,8.425537,0.819824,3.215576,3.862305,9.823242,39.006835,68.060791,54.607178,55.891357,62.385742,64.061768,61.809082,72.044189,78.759277,125.201661,86.556885,99.334229,104.277832,99.572266</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.347829,0.415396,0.301494,0.320110,0.070427,0.327779,0.031802,0.124664,0.149701,0.380027,1.493096,2.577767,2.079275,2.128692,2.369406,2.431907,2.349994,2.730032,2.978691,4.655756,3.266803,3.732770,3.912541,3.743909</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1.788327892924973</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>2584.937012,2582.305664,2582.281006,2579.533203,2577.585938,2574.342285,2572.844482,2570.656738,2572.088867,2569.591309,2567.844482,2566.470215,2564.636963,2563.531250,2563.921143,2563.952393,2561.977051,2560.764160,2558.833984,2558.158936,2557.426758,2554.593018,2555.020264,2554.995117</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>2577.472168,2572.412354,2566.924072,2563.412109,2558.150146,2554.154053,2552.620361,2547.495605,2546.590088,2544.607422,2541.027588,2539.863281,2536.902100,2533.806152,2531.955566,2531.709717,2527.728271,2525.877930,2521.580322,2519.687744,2517.528564,2514.007812,2513.112793,2511.974609</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:40</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2659.450439,2658.208252,2657.647461,2658.179688,2657.043945,2656.774170,2656.597656,2655.362061,2655.253418,2653.614990,2652.888184,2652.510742,2651.473389,2650.348145,2651.171631,2650.428223,2649.916748,2648.322266,2647.384521,2646.452148,2645.779541,2643.833984,2643.650879,2641.998047</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2658.995117,2656.874756,2656.939697,2656.456299,2652.884766,2652.755127,2649.679932,2651.949707,2648.212646,2648.997314,2646.424072,2644.480957,2642.055176,2643.557617,2642.268555,2642.409180,2636.919434,2638.250488,2636.077881,2634.965576,2632.701660,2632.422852,2631.016602,2629.523682</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2643.244629,2637.959717,2631.229004,2628.776367,2622.822266,2619.569336,2615.914062,2610.750977,2609.563721,2605.202637,2600.816650,2597.550537,2595.551514,2591.398926,2588.541992,2586.805176,2583.081055,2580.131348,2573.973389,2568.397705,2567.150879,2562.762939,2559.522461,2557.502930</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2650.287109,2646.744385,2642.170410,2640.907959,2636.412109,2634.003418,2633.171143,2629.602295,2628.167236,2625.306152,2621.814941,2621.301758,2618.040527,2614.473877,2613.240723,2613.435059,2610.633789,2608.120117,2603.905273,2602.485352,2600.114258,2596.094238,2595.220703,2593.032715</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>2641.998046875</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2730.760009765625</v>
+      </c>
+      <c r="H65" t="n">
+        <v>88.761962890625</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3.250449053494205</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.020315451902693</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:36</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2698.8701171875</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>2659.450439,2658.208252,2657.647461,2658.179688,2657.043945,2656.774170,2656.597656,2655.362061,2655.253418,2653.614990,2652.888184,2652.510742,2651.473389,2650.348145,2651.171631,2650.428223,2649.916748,2648.322266,2647.384521,2646.452148,2645.779541,2643.833984,2643.650879,2641.998047</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2664.639893,2662.790039,2660.639893,2696.020020,2720.040039,2715.219971,2724.530029,2734.860107,2730.750000,2736.389893,2755.239990,2754.590088,2743.429932,2758.139893,2762.050049,2784.560059,2768.159912,2778.600098,2775.580078,2754.389893,2748.219971,2739.280029,2738.810059,2730.760010</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>5.189454,4.581787,2.992432,37.840332,62.996094,58.445801,67.932373,79.498046,75.496582,82.774903,102.351806,102.079346,91.956543,107.791748,110.878418,134.131836,118.243164,130.277832,128.195557,107.937745,102.440430,95.446045,95.159180,88.761963</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.194753,0.172067,0.112470,1.403563,2.315999,2.152525,2.493361,2.906841,2.764683,3.024967,3.714805,3.705791,3.351882,3.908132,4.014352,4.816985,4.271544,4.688614,4.618694,3.918753,3.727519,3.484348,3.474472,3.250449</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>3.020315451902693</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>2658.995117,2656.874756,2656.939697,2656.456299,2652.884766,2652.755127,2649.679932,2651.949707,2648.212646,2648.997314,2646.424072,2644.480957,2642.055176,2643.557617,2642.268555,2642.409180,2636.919434,2638.250488,2636.077881,2634.965576,2632.701660,2632.422852,2631.016602,2629.523682</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>2650.287109,2646.744385,2642.170410,2640.907959,2636.412109,2634.003418,2633.171143,2629.602295,2628.167236,2625.306152,2621.814941,2621.301758,2618.040527,2614.473877,2613.240723,2613.435059,2610.633789,2608.120117,2603.905273,2602.485352,2600.114258,2596.094238,2595.220703,2593.032715</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:36</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2730.444336,2727.060303,2725.997070,2726.299561,2723.827881,2722.078369,2721.376465,2721.037109,2720.963867,2719.361572,2717.678711,2716.997559,2714.213135,2712.636230,2713.880859,2712.450195,2711.084961,2709.322510,2706.484375,2703.007324,2702.427246,2701.032715,2700.336426,2698.870117</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2725.975830,2723.603271,2721.660889,2725.271484,2719.753662,2715.564453,2713.209229,2714.149170,2714.127441,2714.068848,2711.341553,2704.900635,2702.220947,2701.787109,2702.462158,2702.583496,2698.224609,2697.784424,2694.124023,2691.250244,2691.184570,2689.088135,2682.723145,2684.187744</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2705.822998,2698.866943,2691.211426,2687.662109,2680.623535,2675.395508,2669.544434,2664.884033,2663.081055,2657.713867,2651.167725,2646.570068,2642.716797,2638.629883,2634.093750,2630.886719,2625.167480,2621.942871,2612.411621,2603.878906,2601.504639,2597.202148,2592.673584,2592.309326</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2715.868652,2709.644531,2704.406494,2703.133789,2697.912842,2692.772461,2691.062744,2686.815186,2687.309814,2683.141357,2678.199707,2676.425781,2670.223145,2667.971924,2666.042480,2663.847656,2660.998291,2656.473633,2650.008057,2645.370850,2642.492188,2638.679199,2636.319824,2634.616699</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>2698.8701171875</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2780.360107421875</v>
+      </c>
+      <c r="H66" t="n">
+        <v>81.489990234375</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.930914956549914</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.28528917182685</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2775.223876953125</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>2730.444336,2727.060303,2725.997070,2726.299561,2723.827881,2722.078369,2721.376465,2721.037109,2720.963867,2719.361572,2717.678711,2716.997559,2714.213135,2712.636230,2713.880859,2712.450195,2711.084961,2709.322510,2706.484375,2703.007324,2702.427246,2701.032715,2700.336426,2698.870117</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2732.679932,2730.010010,2726.129883,2748.330078,2750.209961,2741.590088,2741.620117,2755.800049,2758.030029,2742.620117,2743.889893,2745.719971,2753.949951,2752.260010,2751.860107,2751.360107,2747.310059,2752.800049,2753.379883,2759.610107,2753.969971,2762.090088,2773.679932,2780.360107</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2.235596,2.949707,0.132813,22.030517,26.382080,19.511719,20.243652,34.762940,37.066162,23.258545,26.211182,28.722412,39.736816,39.623780,37.979248,38.909912,36.225098,43.477539,46.895508,56.602783,51.542725,61.057373,73.343506,81.489990</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.081810,0.108047,0.004872,0.801596,0.959275,0.711694,0.738383,1.261446,1.343936,0.848041,0.955256,1.046079,1.442903,1.439682,1.380130,1.414206,1.318566,1.579393,1.703198,2.051115,1.871579,2.210550,2.644267,2.930915</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1.28528917182685</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>2725.975830,2723.603271,2721.660889,2725.271484,2719.753662,2715.564453,2713.209229,2714.149170,2714.127441,2714.068848,2711.341553,2704.900635,2702.220947,2701.787109,2702.462158,2702.583496,2698.224609,2697.784424,2694.124023,2691.250244,2691.184570,2689.088135,2682.723145,2684.187744</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>2715.868652,2709.644531,2704.406494,2703.133789,2697.912842,2692.772461,2691.062744,2686.815186,2687.309814,2683.141357,2678.199707,2676.425781,2670.223145,2667.971924,2666.042480,2663.847656,2660.998291,2656.473633,2650.008057,2645.370850,2642.492188,2638.679199,2636.319824,2634.616699</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2780.638428,2780.437988,2783.016602,2785.537598,2785.797363,2786.129395,2786.558838,2785.257324,2787.164062,2784.951416,2783.919678,2783.788574,2781.813965,2779.681641,2781.691895,2780.500977,2782.156982,2779.811279,2779.374512,2776.632324,2777.156006,2775.697998,2775.500488,2775.223877</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2778.294434,2778.199707,2779.840820,2782.532715,2785.604736,2781.988525,2782.171875,2780.830566,2784.255371,2782.224609,2780.581055,2775.449219,2775.981934,2774.822266,2774.686035,2774.957275,2772.936035,2771.641602,2773.742188,2769.073730,2770.354980,2769.768066,2765.333984,2767.763184</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2767.980469,2764.077881,2760.752441,2760.403564,2756.557617,2753.977051,2751.692871,2747.055664,2746.093750,2741.335693,2737.711426,2734.670898,2731.696777,2726.696777,2725.766357,2724.712402,2722.640625,2720.272217,2715.861816,2709.069336,2709.401367,2705.219727,2702.590332,2702.868652</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2773.460938,2770.252197,2769.730225,2771.411133,2768.704102,2766.982178,2767.349609,2763.392090,2764.666016,2760.302734,2757.689453,2757.342773,2753.504883,2748.559082,2749.409912,2748.648926,2748.394043,2744.715576,2742.179199,2739.104980,2737.661621,2734.296387,2734.310059,2732.089111</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>2775.223876953125</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2674.389892578125</v>
+      </c>
+      <c r="H67" t="n">
+        <v>100.833984375</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3.77035467621348</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.127332909581746</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:11</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2682.615478515625</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>2780.638428,2780.437988,2783.016602,2785.537598,2785.797363,2786.129395,2786.558838,2785.257324,2787.164062,2784.951416,2783.919678,2783.788574,2781.813965,2779.681641,2781.691895,2780.500977,2782.156982,2779.811279,2779.374512,2776.632324,2777.156006,2775.697998,2775.500488,2775.223877</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2757.399902,2754.040039,2742.580078,2734.639893,2733.149902,2737.399902,2727.419922,2721.189941,2715.189941,2675.949951,2656.100098,2660.290039,2667.600098,2668.469971,2678.100098,2671.120117,2677.129883,2689.530029,2682.530029,2682.280029,2674.580078,2685.090088,2676.179932,2674.389893</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>23.238526,26.397949,40.436524,50.897705,52.647461,48.729493,59.138916,64.067383,71.974121,109.001465,127.819580,123.498535,114.213867,111.211670,103.591797,109.380860,105.027099,90.281250,96.844483,94.352295,102.575928,90.607910,99.320556,100.833984</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.842770,0.958517,1.474397,1.861221,1.926256,1.780138,2.168310,2.354388,2.650795,4.073375,4.812303,4.642296,4.281521,4.167619,3.868108,4.094944,3.923123,3.356767,3.610192,3.517615,3.835216,3.374483,3.711281,3.770355</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>3.127332909581746</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>2778.294434,2778.199707,2779.840820,2782.532715,2785.604736,2781.988525,2782.171875,2780.830566,2784.255371,2782.224609,2780.581055,2775.449219,2775.981934,2774.822266,2774.686035,2774.957275,2772.936035,2771.641602,2773.742188,2769.073730,2770.354980,2769.768066,2765.333984,2767.763184</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>2773.460938,2770.252197,2769.730225,2771.411133,2768.704102,2766.982178,2767.349609,2763.392090,2764.666016,2760.302734,2757.689453,2757.342773,2753.504883,2748.559082,2749.409912,2748.648926,2748.394043,2744.715576,2742.179199,2739.104980,2737.661621,2734.296387,2734.310059,2732.089111</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:11</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2673.708984,2673.333496,2674.088379,2674.868652,2673.687988,2673.831299,2675.338867,2675.234375,2675.747559,2675.008789,2676.156250,2677.353027,2678.032715,2678.230713,2679.986572,2680.051514,2681.220215,2681.948486,2682.588867,2682.711182,2682.175537,2682.438232,2683.163574,2682.615479</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2670.098877,2672.816406,2670.507324,2671.680664,2674.262695,2674.335449,2673.614746,2671.342285,2675.162842,2675.178223,2671.292969,2670.612305,2673.033936,2674.907227,2677.270020,2676.360352,2674.945068,2676.441895,2680.372070,2676.170410,2676.426025,2675.139893,2676.906250,2677.124512</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2656.186035,2652.579346,2648.525879,2647.050537,2642.322754,2638.467529,2637.009277,2632.904785,2629.801758,2626.870117,2623.741455,2623.327881,2624.023682,2622.045898,2619.856201,2619.503662,2616.950195,2616.419434,2611.344238,2610.147461,2607.079590,2607.296387,2605.301514,2604.558350</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2663.276367,2660.015381,2658.003418,2657.562256,2653.338379,2650.866211,2650.533203,2647.753174,2646.696533,2644.047119,2642.514404,2644.367432,2643.574219,2641.575439,2642.528809,2642.178467,2640.896240,2639.644531,2639.170654,2638.908447,2637.256104,2635.939941,2637.574707,2634.933838</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>2682.615478515625</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2680.60009765625</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.015380859375</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.0751839433691405</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.4433530921339006</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:29</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2684.186279296875</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>2673.708984,2673.333496,2674.088379,2674.868652,2673.687988,2673.831299,2675.338867,2675.234375,2675.747559,2675.008789,2676.156250,2677.353027,2678.032715,2678.230713,2679.986572,2680.051514,2681.220215,2681.948486,2682.588867,2682.711182,2682.175537,2682.438232,2683.163574,2682.615479</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2681.860107,2685.610107,2692.979980,2668.360107,2641.310059,2647.639893,2646.669922,2647.939941,2669.540039,2657.030029,2682.620117,2686.639893,2668.860107,2689.290039,2696.120117,2687.439941,2686.090088,2684.689941,2687.350098,2689.729980,2689.129883,2675.959961,2678.250000,2680.600098</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>8.151123,12.276611,18.891601,6.508545,32.377929,26.191406,28.668945,27.294434,6.207520,17.978760,6.463867,9.286866,9.172608,11.059326,16.133545,7.388427,4.869873,2.741455,4.761231,7.018798,6.954346,6.478271,4.913574,2.015381</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.303935,0.457126,0.701513,0.243916,1.225828,0.989236,1.083208,1.030780,0.232531,0.676649,0.240954,0.345668,0.343690,0.411236,0.598399,0.274924,0.181300,0.102114,0.177172,0.260948,0.258610,0.242091,0.183462,0.075184</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.4433530921339006</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>2670.098877,2672.816406,2670.507324,2671.680664,2674.262695,2674.335449,2673.614746,2671.342285,2675.162842,2675.178223,2671.292969,2670.612305,2673.033936,2674.907227,2677.270020,2676.360352,2674.945068,2676.441895,2680.372070,2676.170410,2676.426025,2675.139893,2676.906250,2677.124512</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>2663.276367,2660.015381,2658.003418,2657.562256,2653.338379,2650.866211,2650.533203,2647.753174,2646.696533,2644.047119,2642.514404,2644.367432,2643.574219,2641.575439,2642.528809,2642.178467,2640.896240,2639.644531,2639.170654,2638.908447,2637.256104,2635.939941,2637.574707,2634.933838</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:29</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2680.118652,2679.845459,2680.433105,2681.124512,2679.910645,2679.428223,2680.873047,2680.232666,2681.816406,2681.450928,2682.868896,2683.968750,2685.239258,2684.107910,2685.226074,2685.074219,2685.679199,2685.588135,2685.369873,2684.833008,2684.102295,2683.351074,2684.593262,2684.186279</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2678.025879,2679.214111,2679.296387,2678.128906,2679.597656,2680.974121,2679.928711,2677.607666,2679.779785,2681.246094,2679.544189,2676.314453,2679.909668,2681.066650,2681.242188,2681.189697,2679.933838,2680.354736,2682.761475,2677.437744,2678.493164,2677.665527,2680.553711,2679.270264</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2663.367188,2659.699951,2656.397705,2655.251465,2650.503662,2646.192627,2645.461426,2641.842285,2639.311523,2636.704102,2634.968750,2634.237549,2634.237549,2629.788330,2628.153320,2626.221924,2624.946777,2623.870117,2618.612793,2615.221436,2612.712402,2609.696777,2609.586426,2609.164795</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2670.723145,2667.222412,2665.438477,2664.939941,2661.538574,2658.303711,2658.100098,2655.125488,2655.552490,2652.791260,2652.552246,2653.325684,2653.218506,2649.375977,2649.825195,2649.197510,2648.416504,2646.956543,2645.277588,2643.263916,2641.348877,2638.116211,2640.223633,2638.390137</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>2684.186279296875</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2687.739990234375</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.5537109375</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.1322192976408448</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.3757596577625657</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:21</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2697.8671875</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>2680.118652,2679.845459,2680.433105,2681.124512,2679.910645,2679.428223,2680.873047,2680.232666,2681.816406,2681.450928,2682.868896,2683.968750,2685.239258,2684.107910,2685.226074,2685.074219,2685.679199,2685.588135,2685.369873,2684.833008,2684.102295,2683.351074,2684.593262,2684.186279</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2679.709961,2674.239990,2672.229980,2690.590088,2704.000000,2713.770020,2717.040039,2716.770020,2694.489990,2695.429932,2686.060059,2682.909912,2685.370117,2692.979980,2692.949951,2683.840088,2681.149902,2691.310059,2691.310059,2686.770020,2692.310059,2690.699951,2687.370117,2687.739990</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.408691,5.605469,8.203125,9.465576,24.089355,34.341797,36.166992,36.537354,12.673584,13.979004,3.191163,1.058838,0.130859,8.872070,7.723877,1.234131,4.529297,5.721924,5.940186,1.937012,8.207764,7.348877,2.776855,3.553711</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.015251,0.209610,0.306977,0.351803,0.890879,1.265465,1.331117,1.344882,0.470352,0.518619,0.118805,0.039466,0.004873,0.329452,0.286818,0.045984,0.168931,0.212607,0.220717,0.072094,0.304860,0.273121,0.103330,0.132219</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.3757596577625657</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>2678.025879,2679.214111,2679.296387,2678.128906,2679.597656,2680.974121,2679.928711,2677.607666,2679.779785,2681.246094,2679.544189,2676.314453,2679.909668,2681.066650,2681.242188,2681.189697,2679.933838,2680.354736,2682.761475,2677.437744,2678.493164,2677.665527,2680.553711,2679.270264</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>2670.723145,2667.222412,2665.438477,2664.939941,2661.538574,2658.303711,2658.100098,2655.125488,2655.552490,2652.791260,2652.552246,2653.325684,2653.218506,2649.375977,2649.825195,2649.197510,2648.416504,2646.956543,2645.277588,2643.263916,2641.348877,2638.116211,2640.223633,2638.390137</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:21</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2689.482910,2689.290283,2689.994629,2690.703613,2691.260010,2691.887695,2693.961426,2692.926025,2694.240479,2694.403076,2694.895996,2695.395020,2696.121094,2695.586914,2697.370361,2697.540527,2698.290527,2698.208984,2698.749268,2698.781982,2698.693115,2698.277588,2699.046387,2697.867188</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2689.979004,2690.101074,2688.818359,2688.489502,2692.476562,2692.329346,2694.931641,2690.638184,2694.804443,2693.995361,2693.616211,2692.706055,2693.048096,2694.033203,2694.192627,2694.147217,2695.786133,2697.081299,2698.658691,2694.717041,2696.108398,2692.609375,2697.010498,2694.717773</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2677.343750,2675.582520,2673.092773,2673.763184,2670.656006,2668.253174,2669.836914,2667.034180,2664.252930,2662.501465,2660.599854,2659.145020,2657.647949,2655.944824,2655.655273,2654.471680,2652.986816,2651.425293,2648.081055,2647.694824,2646.170654,2644.626465,2644.454346,2642.403076</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2682.906494,2681.024658,2680.639404,2680.447021,2678.547607,2677.879639,2678.892334,2676.258301,2677.501953,2674.972900,2673.459961,2673.778564,2673.068604,2670.854492,2673.519775,2672.808350,2671.610352,2670.620605,2669.531250,2670.113281,2668.601074,2667.690918,2668.334473,2666.113037</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>2697.8671875</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2691.510009765625</v>
+      </c>
+      <c r="H70" t="n">
+        <v>6.357177734375</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.2361937243892539</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.2304073297937242</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:19</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2691.11572265625</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>2689.482910,2689.290283,2689.994629,2690.703613,2691.260010,2691.887695,2693.961426,2692.926025,2694.240479,2694.403076,2694.895996,2695.395020,2696.121094,2695.586914,2697.370361,2697.540527,2698.290527,2698.208984,2698.749268,2698.781982,2698.693115,2698.277588,2699.046387,2697.867188</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2686.149902,2685.060059,2690.439941,2690.429932,2682.219971,2686.919922,2688.989990,2688.399902,2686.229980,2688.540039,2692.500000,2691.010010,2690.000000,2684.620117,2683.959961,2676.250000,2685.909912,2688.149902,2695.689941,2692.899902,2701.110107,2697.300049,2695.870117,2691.510010</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>3.333008,4.230224,0.445312,0.273681,9.040039,4.967773,4.971436,4.526123,8.010499,5.863037,2.395996,4.385010,6.121094,10.966797,13.410400,21.290527,12.380615,10.059082,3.059327,5.882080,2.416992,0.977539,3.176270,6.357178</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.124081,0.157547,0.016552,0.010172,0.337036,0.184887,0.184881,0.168357,0.298206,0.218075,0.088988,0.162950,0.227550,0.408505,0.499650,0.795536,0.460947,0.374201,0.113490,0.218429,0.089481,0.036241,0.117820,0.236194</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.2304073297937242</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>2689.979004,2690.101074,2688.818359,2688.489502,2692.476562,2692.329346,2694.931641,2690.638184,2694.804443,2693.995361,2693.616211,2692.706055,2693.048096,2694.033203,2694.192627,2694.147217,2695.786133,2697.081299,2698.658691,2694.717041,2696.108398,2692.609375,2697.010498,2694.717773</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>2682.906494,2681.024658,2680.639404,2680.447021,2678.547607,2677.879639,2678.892334,2676.258301,2677.501953,2674.972900,2673.459961,2673.778564,2673.068604,2670.854492,2673.519775,2672.808350,2671.610352,2670.620605,2669.531250,2670.113281,2668.601074,2667.690918,2668.334473,2666.113037</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:19</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2694.272217,2692.689453,2693.595947,2694.294922,2693.630127,2693.055664,2694.668457,2693.944824,2694.067627,2693.327881,2692.996094,2692.349365,2692.762695,2691.497314,2691.941895,2691.880127,2692.659668,2692.121338,2691.987793,2691.329102,2691.931885,2691.580566,2691.276367,2691.115723</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2694.688721,2692.160156,2690.862549,2692.722168,2694.726074,2691.740234,2692.801025,2692.677979,2694.175293,2691.145508,2691.134033,2688.568848,2689.376709,2688.339600,2688.339600,2687.815430,2690.654541,2687.645996,2689.967529,2686.255371,2686.883301,2686.314453,2685.705566,2684.890137</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2685.659180,2683.391357,2681.841797,2682.886230,2679.201416,2676.616699,2678.531494,2677.267578,2672.353027,2670.657715,2668.159912,2666.875000,2664.531738,2663.089111,2660.896484,2659.979736,2657.707031,2656.132324,2651.112061,2649.491455,2648.220459,2646.642822,2644.750977,2642.695801</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2689.963379,2687.646484,2687.797852,2687.441406,2685.240234,2683.590820,2684.601562,2683.333740,2683.562012,2681.035645,2679.014648,2677.472168,2678.111816,2674.958252,2675.410400,2674.897949,2673.800781,2672.440918,2670.374023,2669.675293,2669.076660,2666.813232,2666.250732,2665.370605</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>2691.11572265625</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2655.239990234375</v>
+      </c>
+      <c r="H71" t="n">
+        <v>35.875732421875</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.351129560936911</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.622190336725065</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:03</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2661.39599609375</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>2694.272217,2692.689453,2693.595947,2694.294922,2693.630127,2693.055664,2694.668457,2693.944824,2694.067627,2693.327881,2692.996094,2692.349365,2692.762695,2691.497314,2691.941895,2691.880127,2692.659668,2692.121338,2691.987793,2691.329102,2691.931885,2691.580566,2691.276367,2691.115723</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2706.479980,2717.709961,2713.409912,2715.360107,2709.550049,2709.080078,2706.760010,2709.370117,2687.399902,2689.500000,2685.899902,2690.590088,2697.639893,2690.929932,2685.530029,2684.070068,2675.239990,2687.949951,2673.790039,2656.719971,2651.790039,2651.790039,2657.969971,2655.239990</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>12.207763,25.020508,19.813965,21.065185,15.919922,16.024414,12.091553,15.425293,6.667725,3.827881,7.096192,1.759277,4.877198,0.567382,6.411866,7.810059,17.419678,4.171387,18.197754,34.609131,40.141846,39.790527,33.306396,35.875733</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.451057,0.920647,0.730224,0.775779,0.587549,0.591508,0.446717,0.569331,0.248111,0.142327,0.264202,0.065386,0.180795,0.021085,0.238756,0.290978,0.651144,0.155188,0.680598,1.302702,1.513764,1.500516,1.253076,1.351130</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.622190336725065</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>2694.688721,2692.160156,2690.862549,2692.722168,2694.726074,2691.740234,2692.801025,2692.677979,2694.175293,2691.145508,2691.134033,2688.568848,2689.376709,2688.339600,2688.339600,2687.815430,2690.654541,2687.645996,2689.967529,2686.255371,2686.883301,2686.314453,2685.705566,2684.890137</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>2689.963379,2687.646484,2687.797852,2687.441406,2685.240234,2683.590820,2684.601562,2683.333740,2683.562012,2681.035645,2679.014648,2677.472168,2678.111816,2674.958252,2675.410400,2674.897949,2673.800781,2672.440918,2670.374023,2669.675293,2669.076660,2666.813232,2666.250732,2665.370605</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:03</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2656.390625,2654.969971,2655.296387,2655.554688,2655.574707,2655.206787,2655.906494,2655.597168,2655.046143,2655.310059,2655.534668,2655.746338,2657.304688,2656.845215,2657.307861,2657.868164,2659.227051,2659.336670,2659.317871,2659.514648,2660.030762,2659.991455,2660.956055,2661.395996</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2656.413086,2656.062988,2654.335205,2655.311279,2656.933838,2654.745117,2656.366699,2653.802734,2656.530029,2655.536133,2655.733154,2655.887207,2653.462402,2656.052246,2655.867432,2656.835205,2658.628418,2657.347656,2660.443604,2656.451172,2658.754883,2656.786377,2659.515137,2657.280518</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2644.778076,2640.573730,2637.694824,2636.055420,2632.598389,2629.094727,2628.804688,2626.914795,2622.224609,2619.782227,2618.201416,2617.437988,2617.629395,2615.884033,2614.139648,2613.641846,2612.054443,2610.580566,2605.450195,2604.482910,2603.732422,2602.783691,2602.821289,2601.378418</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2650.523438,2646.724854,2645.197754,2643.582764,2641.351074,2639.039062,2638.256104,2636.374023,2635.876465,2633.294434,2631.986816,2631.753906,2633.090820,2630.907227,2631.667725,2631.921387,2630.340820,2628.900635,2627.126953,2627.554199,2627.439941,2625.566162,2626.912598,2626.070557</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>2661.39599609375</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2671.3798828125</v>
+      </c>
+      <c r="H72" t="n">
+        <v>9.98388671875</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.373735191426189</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.6579942693998535</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:48</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2686.7529296875</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>2656.390625,2654.969971,2655.296387,2655.554688,2655.574707,2655.206787,2655.906494,2655.597168,2655.046143,2655.310059,2655.534668,2655.746338,2657.304688,2656.845215,2657.307861,2657.868164,2659.227051,2659.336670,2659.317871,2659.514648,2660.030762,2659.991455,2660.956055,2661.395996</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2649.000000,2642.879883,2649.669922,2639.750000,2654.939941,2667.989990,2690.219971,2689.860107,2666.530029,2677.870117,2686.139893,2694.530029,2698.639893,2672.409912,2681.639893,2673.159912,2686.469971,2687.350098,2676.040039,2664.370117,2656.370117,2664.159912,2666.689941,2671.379883</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>7.390625,12.090088,5.626465,15.804688,0.634766,12.783203,34.313477,34.262939,11.483886,22.560058,30.605225,38.783691,41.335205,15.564697,24.332032,15.291748,27.242920,28.013428,16.722168,4.855469,3.660645,4.168457,5.733886,9.983887</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.278997,0.457459,0.212346,0.598719,0.023909,0.479132,1.275490,1.273781,0.430668,0.842463,1.139376,1.439349,1.531705,0.582422,0.907356,0.572048,1.014079,1.042418,0.624885,0.182237,0.137806,0.156464,0.215019,0.373735</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.6579942693998535</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>2656.413086,2656.062988,2654.335205,2655.311279,2656.933838,2654.745117,2656.366699,2653.802734,2656.530029,2655.536133,2655.733154,2655.887207,2653.462402,2656.052246,2655.867432,2656.835205,2658.628418,2657.347656,2660.443604,2656.451172,2658.754883,2656.786377,2659.515137,2657.280518</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>2650.523438,2646.724854,2645.197754,2643.582764,2641.351074,2639.039062,2638.256104,2636.374023,2635.876465,2633.294434,2631.986816,2631.753906,2633.090820,2630.907227,2631.667725,2631.921387,2630.340820,2628.900635,2627.126953,2627.554199,2627.439941,2625.566162,2626.912598,2626.070557</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:48</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2671.636719,2671.090820,2672.285645,2673.675537,2675.542236,2676.475098,2677.774170,2678.821289,2679.390869,2679.987793,2680.248047,2681.118164,2682.707520,2682.153076,2683.439453,2683.604004,2685.192871,2684.268555,2685.323730,2685.140137,2685.418701,2685.379150,2685.906738,2686.752930</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2672.135498,2673.261230,2672.132568,2673.824219,2677.249512,2675.327393,2678.596680,2679.066650,2680.985596,2680.442627,2681.222168,2681.551270,2680.792480,2684.024658,2684.166748,2683.159912,2684.894287,2686.272949,2687.031250,2682.967529,2685.721924,2683.332031,2688.516602,2683.758789</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2658.306396,2655.404297,2653.952881,2654.643066,2653.001465,2651.558105,2652.421875,2651.534668,2648.724609,2646.806396,2646.039795,2645.494141,2645.725586,2643.388184,2643.616211,2642.626953,2642.894531,2641.968262,2638.622803,2637.471191,2637.701660,2635.727051,2635.211426,2634.578369</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2664.172607,2661.318359,2661.279297,2660.982422,2661.035156,2660.260986,2661.884766,2661.032227,2661.054688,2659.738037,2658.024902,2659.004883,2660.238525,2656.999023,2658.824951,2658.517090,2658.098877,2656.989258,2656.012451,2656.633301,2656.417236,2654.351318,2654.611328,2654.733887</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>2686.7529296875</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2666.570068359375</v>
+      </c>
+      <c r="H73" t="n">
+        <v>20.182861328125</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.7568847174731336</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.8243904604399435</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:26</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2666.545654296875</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>2671.636719,2671.090820,2672.285645,2673.675537,2675.542236,2676.475098,2677.774170,2678.821289,2679.390869,2679.987793,2680.248047,2681.118164,2682.707520,2682.153076,2683.439453,2683.604004,2685.192871,2684.268555,2685.323730,2685.140137,2685.418701,2685.379150,2685.906738,2686.752930</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2705.719971,2711.100098,2708.389893,2716.620117,2713.649902,2731.250000,2736.139893,2726.939941,2709.939941,2673.219971,2674.979980,2672.830078,2694.739990,2688.310059,2688.429932,2678.250000,2680.649902,2677.060059,2671.280029,2671.080078,2673.320068,2670.979980,2668.810059,2666.570068</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>34.083252,40.009278,36.104248,42.944580,38.107666,54.774902,58.365723,48.118652,30.549072,6.767822,5.268067,8.288086,12.032470,6.156983,4.990479,5.354004,4.542969,7.208496,14.043701,14.060059,12.098633,14.399170,17.096679,20.182862</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.259674,1.475758,1.333052,1.580809,1.404296,2.005488,2.133141,1.764566,1.127297,0.253171,0.196939,0.310087,0.446517,0.229028,0.185628,0.199907,0.169473,0.269269,0.525729,0.526381,0.452570,0.539097,0.640611,0.756885</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.8243904604399435</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>2672.135498,2673.261230,2672.132568,2673.824219,2677.249512,2675.327393,2678.596680,2679.066650,2680.985596,2680.442627,2681.222168,2681.551270,2680.792480,2684.024658,2684.166748,2683.159912,2684.894287,2686.272949,2687.031250,2682.967529,2685.721924,2683.332031,2688.516602,2683.758789</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>2664.172607,2661.318359,2661.279297,2660.982422,2661.035156,2660.260986,2661.884766,2661.032227,2661.054688,2659.738037,2658.024902,2659.004883,2660.238525,2656.999023,2658.824951,2658.517090,2658.098877,2656.989258,2656.012451,2656.633301,2656.417236,2654.351318,2654.611328,2654.733887</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:26</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2667.408936,2666.684814,2666.754883,2666.954102,2667.341064,2667.729980,2667.833740,2666.986328,2666.850586,2666.560547,2665.477051,2665.168213,2665.541016,2664.805908,2666.069092,2666.112793,2667.245117,2666.315918,2666.777832,2666.711914,2666.329590,2666.696777,2666.496338,2666.545654</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2668.213867,2668.809570,2667.037598,2666.325195,2668.248535,2667.160156,2668.842285,2666.913086,2666.449219,2667.268066,2667.004395,2664.080566,2664.575684,2666.228760,2666.899902,2666.875488,2667.454102,2666.033936,2666.360840,2665.283691,2666.462402,2664.018066,2668.051025,2664.580078</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2655.286621,2652.652832,2650.164062,2648.717529,2645.580322,2644.076172,2643.527588,2640.082031,2637.959473,2634.703857,2631.614502,2629.643799,2629.248291,2626.990479,2626.364014,2623.957520,2624.466064,2622.529297,2617.927979,2617.182129,2617.044678,2616.164307,2615.571289,2614.540527</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2660.926025,2658.072266,2656.182373,2655.071777,2653.704102,2652.209473,2651.989746,2649.374268,2649.487061,2646.517578,2643.666992,2643.244629,2643.269043,2640.915527,2641.797607,2640.594971,2640.674561,2637.889160,2637.419434,2637.332764,2636.618164,2635.022705,2635.512451,2634.904785</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>2666.545654296875</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2712.570068359375</v>
+      </c>
+      <c r="H74" t="n">
+        <v>46.0244140625</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.696708763373498</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8038264004369564</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:33</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2700.405029296875</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>2667.408936,2666.684814,2666.754883,2666.954102,2667.341064,2667.729980,2667.833740,2666.986328,2666.850586,2666.560547,2665.477051,2665.168213,2665.541016,2664.805908,2666.069092,2666.112793,2667.245117,2666.315918,2666.777832,2666.711914,2666.329590,2666.696777,2666.496338,2666.545654</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2660.739990,2673.610107,2669.820068,2687.389893,2694.270020,2696.709961,2730.590088,2708.580078,2676.739990,2681.780029,2694.290039,2681.860107,2677.989990,2668.870117,2680.889893,2682.870117,2685.360107,2683.929932,2683.040039,2688.050049,2685.330078,2693.729980,2705.370117,2712.570068</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6.668946,6.925293,3.065185,20.435791,26.928956,28.979981,62.756348,41.593750,9.889404,15.219482,28.812988,16.691894,12.448974,4.064209,14.820801,16.757324,18.114990,17.614014,16.262207,21.338135,19.000488,27.033203,38.873779,46.024414</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.250643,0.259024,0.114809,0.760433,0.999490,1.074642,2.298271,1.535629,0.369457,0.567514,1.069409,0.622400,0.464863,0.152282,0.552831,0.624604,0.674583,0.656277,0.606111,0.793815,0.707566,1.003560,1.436912,1.696709</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8038264004369564</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>2668.213867,2668.809570,2667.037598,2666.325195,2668.248535,2667.160156,2668.842285,2666.913086,2666.449219,2667.268066,2667.004395,2664.080566,2664.575684,2666.228760,2666.899902,2666.875488,2667.454102,2666.033936,2666.360840,2665.283691,2666.462402,2664.018066,2668.051025,2664.580078</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>2660.926025,2658.072266,2656.182373,2655.071777,2653.704102,2652.209473,2651.989746,2649.374268,2649.487061,2646.517578,2643.666992,2643.244629,2643.269043,2640.915527,2641.797607,2640.594971,2640.674561,2637.889160,2637.419434,2637.332764,2636.618164,2635.022705,2635.512451,2634.904785</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:33</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2709.866699,2708.061035,2706.749512,2706.339844,2705.743896,2705.788330,2705.782227,2704.200439,2703.792480,2703.528320,2701.866699,2701.705322,2701.261963,2700.403809,2701.051758,2700.502441,2701.370361,2700.813721,2700.197754,2700.935547,2699.894531,2699.974854,2699.560059,2700.405029</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2711.420410,2709.471191,2705.478027,2706.462646,2707.672852,2704.434082,2705.015869,2703.803711,2703.419922,2701.770996,2701.726074,2698.736816,2699.250244,2700.769531,2699.651123,2699.504150,2700.101562,2698.176025,2700.433594,2698.555664,2697.770020,2697.427246,2698.558350,2697.391357</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2691.139648,2686.306396,2681.338135,2680.192383,2677.038574,2676.277832,2675.723633,2672.077881,2670.552979,2669.358643,2666.476562,2664.150146,2662.309326,2661.555664,2661.453369,2660.432373,2661.364258,2661.106445,2657.667480,2657.354736,2656.472168,2656.644531,2655.668945,2656.212402</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2698.813477,2694.656250,2690.659912,2689.674805,2686.874023,2685.819580,2685.775635,2683.087891,2682.709229,2681.265381,2678.114746,2677.469238,2677.489746,2674.874023,2675.884766,2676.015625,2676.655273,2675.782471,2674.869629,2674.260742,2672.937744,2672.516602,2672.158203,2673.025879</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>2700.405029296875</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2732.7900390625</v>
+      </c>
+      <c r="H75" t="n">
+        <v>32.385009765625</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.18505297892314</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.4833762407275464</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:09</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2721.50146484375</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>2709.866699,2708.061035,2706.749512,2706.339844,2705.743896,2705.788330,2705.782227,2704.200439,2703.792480,2703.528320,2701.866699,2701.705322,2701.261963,2700.403809,2701.051758,2700.502441,2701.370361,2700.813721,2700.197754,2700.935547,2699.894531,2699.974854,2699.560059,2700.405029</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2713.909912,2676.239990,2685.840088,2689.830078,2700.520020,2705.760010,2692.260010,2697.419922,2689.189941,2681.750000,2679.120117,2700.199951,2699.159912,2698.550049,2697.580078,2692.520020,2702.000000,2705.500000,2706.659912,2714.629883,2719.889893,2718.570068,2741.979980,2732.790039</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.043213,31.821045,20.909424,16.509766,5.223876,0.028320,13.522217,6.780517,14.602539,21.778320,22.746582,1.505371,2.102051,1.853760,3.471680,7.982421,0.629639,4.686279,6.462158,13.694336,19.995362,18.595214,42.419921,32.385010</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.148981,1.189021,0.778506,0.613785,0.193440,0.001047,0.502263,0.251370,0.543009,0.812094,0.849032,0.055750,0.077878,0.068695,0.128696,0.296467,0.023303,0.173213,0.238750,0.504464,0.735153,0.684007,1.547054,1.185053</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.4833762407275464</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>2711.420410,2709.471191,2705.478027,2706.462646,2707.672852,2704.434082,2705.015869,2703.803711,2703.419922,2701.770996,2701.726074,2698.736816,2699.250244,2700.769531,2699.651123,2699.504150,2700.101562,2698.176025,2700.433594,2698.555664,2697.770020,2697.427246,2698.558350,2697.391357</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>2698.813477,2694.656250,2690.659912,2689.674805,2686.874023,2685.819580,2685.775635,2683.087891,2682.709229,2681.265381,2678.114746,2677.469238,2677.489746,2674.874023,2675.884766,2676.015625,2676.655273,2675.782471,2674.869629,2674.260742,2672.937744,2672.516602,2672.158203,2673.025879</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:09</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2728.860352,2726.498047,2725.966553,2725.185059,2724.178711,2723.131836,2722.736816,2721.250488,2721.248535,2720.669434,2720.485107,2720.118652,2719.821289,2719.091064,2719.897217,2719.635986,2720.976318,2721.160400,2720.187012,2721.259033,2720.783691,2721.263184,2721.291992,2721.501465</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2728.447754,2726.003906,2725.049561,2724.072021,2722.976318,2722.503662,2721.333008,2720.734863,2719.012207,2718.399414,2719.187012,2715.470459,2716.566406,2718.134766,2716.935547,2716.980225,2718.635498,2715.743896,2718.047852,2718.140625,2718.309814,2718.130371,2719.272217,2717.440430</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2710.239258,2705.261230,2700.886230,2698.645996,2694.574707,2691.731445,2689.177246,2685.254883,2684.125488,2682.127197,2680.089355,2677.198486,2676.286133,2674.873047,2674.014160,2672.827393,2674.696777,2674.963135,2670.421143,2670.177246,2669.146973,2669.922119,2668.467773,2668.779785</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2718.271729,2713.589844,2710.402344,2709.041748,2705.098633,2702.430664,2701.110107,2698.184082,2698.128906,2696.031982,2693.665039,2693.186523,2692.666504,2690.373535,2691.702393,2691.535889,2693.634277,2693.210205,2691.255127,2690.692871,2689.570557,2689.704346,2689.410645,2689.797119</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>2721.50146484375</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2673.889892578125</v>
+      </c>
+      <c r="H76" t="n">
+        <v>47.611572265625</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.780610802179241</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.31724297051428</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:01:59</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2684.559326171875</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>2728.860352,2726.498047,2725.966553,2725.185059,2724.178711,2723.131836,2722.736816,2721.250488,2721.248535,2720.669434,2720.485107,2720.118652,2719.821289,2719.091064,2719.897217,2719.635986,2720.976318,2721.160400,2720.187012,2721.259033,2720.783691,2721.263184,2721.291992,2721.501465</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2728.110107,2736.229980,2753.090088,2746.570068,2742.620117,2746.199951,2755.010010,2744.280029,2709.340088,2696.929932,2689.669922,2683.949951,2664.399902,2667.290039,2661.209961,2664.810059,2667.530029,2668.139893,2675.949951,2678.969971,2676.520020,2681.610107,2675.530029,2673.889893</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.750245,9.731933,27.123535,21.385009,18.441406,23.068115,32.273194,23.029541,11.908447,23.739502,30.815185,36.168701,55.421387,51.801025,58.687256,54.825927,53.446289,53.020507,44.237061,42.289062,44.263671,39.653077,45.761963,47.611572</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.027501,0.355669,0.985203,0.778608,0.672401,0.840001,1.171437,0.839183,0.439533,0.880242,1.145686,1.347592,2.080070,1.942084,2.205285,2.057405,2.003587,1.987171,1.653135,1.578557,1.653777,1.478704,1.710389,1.780611</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1.31724297051428</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>2728.447754,2726.003906,2725.049561,2724.072021,2722.976318,2722.503662,2721.333008,2720.734863,2719.012207,2718.399414,2719.187012,2715.470459,2716.566406,2718.134766,2716.935547,2716.980225,2718.635498,2715.743896,2718.047852,2718.140625,2718.309814,2718.130371,2719.272217,2717.440430</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>2718.271729,2713.589844,2710.402344,2709.041748,2705.098633,2702.430664,2701.110107,2698.184082,2698.128906,2696.031982,2693.665039,2693.186523,2692.666504,2690.373535,2691.702393,2691.535889,2693.634277,2693.210205,2691.255127,2690.692871,2689.570557,2689.704346,2689.410645,2689.797119</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:01:59</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2675.179688,2676.062988,2677.184814,2677.681641,2677.594238,2677.917969,2678.618408,2677.699951,2677.252441,2676.768311,2677.509521,2677.320557,2676.761230,2676.801270,2677.921631,2678.660156,2679.730469,2681.033936,2681.380615,2681.470215,2681.595215,2683.147217,2683.206787,2684.559326</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2675.151855,2676.501465,2676.542969,2677.509033,2677.397949,2680.254639,2677.201172,2677.634521,2677.240479,2676.837891,2678.282471,2675.714844,2674.501953,2676.887939,2676.349609,2677.680176,2679.718994,2678.856934,2681.006348,2679.764404,2681.681641,2681.321777,2682.033447,2681.464355</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2663.410645,2663.096191,2661.695801,2660.995605,2657.293213,2655.312500,2655.319824,2651.510498,2649.438965,2646.776611,2644.905029,2644.980713,2641.992188,2641.750732,2640.700195,2639.718262,2640.750977,2641.471436,2638.059082,2636.702148,2636.398438,2637.179932,2636.007812,2636.758545</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2669.427490,2668.270996,2667.741455,2667.143555,2664.456055,2663.715576,2663.597656,2660.710938,2661.434570,2658.371338,2657.203613,2657.023193,2656.099121,2655.481445,2656.063477,2656.466309,2656.898926,2656.883789,2657.067139,2657.193359,2656.063721,2655.350342,2655.325439,2656.190918</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>2684.559326171875</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2694.2099609375</v>
+      </c>
+      <c r="H77" t="n">
+        <v>9.650634765625</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.3581990604127558</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.261879182479296</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:21</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2695.66845703125</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>2675.179688,2676.062988,2677.184814,2677.681641,2677.594238,2677.917969,2678.618408,2677.699951,2677.252441,2676.768311,2677.509521,2677.320557,2676.761230,2676.801270,2677.921631,2678.660156,2679.730469,2681.033936,2681.380615,2681.470215,2681.595215,2683.147217,2683.206787,2684.559326</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2679.699951,2681.610107,2682.429932,2680.050049,2682.820068,2684.010010,2682.209961,2681.530029,2683.050049,2681.219971,2681.040039,2688.419922,2684.810059,2685.189941,2686.449951,2685.030029,2686.159912,2686.939941,2692.659912,2694.320068,2692.189941,2694.030029,2691.899902,2694.209961</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>4.520263,5.547119,5.245118,2.368408,5.225830,6.092041,3.591553,3.830078,5.797608,4.451660,3.530518,11.099365,8.048829,8.388671,8.528320,6.369873,6.429443,5.906005,11.279297,12.849853,10.594726,10.882812,8.693115,9.650635</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.168685,0.206858,0.195536,0.088372,0.194789,0.226975,0.133903,0.142832,0.216083,0.166031,0.131685,0.412858,0.299791,0.312405,0.317457,0.237237,0.239354,0.219804,0.418891,0.476924,0.393536,0.403960,0.322936,0.358199</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.261879182479296</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>2675.151855,2676.501465,2676.542969,2677.509033,2677.397949,2680.254639,2677.201172,2677.634521,2677.240479,2676.837891,2678.282471,2675.714844,2674.501953,2676.887939,2676.349609,2677.680176,2679.718994,2678.856934,2681.006348,2679.764404,2681.681641,2681.321777,2682.033447,2681.464355</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>2669.427490,2668.270996,2667.741455,2667.143555,2664.456055,2663.715576,2663.597656,2660.710938,2661.434570,2658.371338,2657.203613,2657.023193,2656.099121,2655.481445,2656.063477,2656.466309,2656.898926,2656.883789,2657.067139,2657.193359,2656.063721,2655.350342,2655.325439,2656.190918</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:21</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2693.331543,2693.802002,2694.307861,2695.177490,2695.184570,2695.820312,2696.276367,2695.466309,2695.259033,2695.124023,2695.357910,2695.401611,2694.703613,2694.080078,2694.515381,2694.543945,2694.521484,2694.520020,2694.931885,2694.630371,2695.035400,2695.466797,2695.491455,2695.668457</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2692.884521,2695.052734,2694.552002,2694.608398,2695.383057,2696.531250,2696.734619,2695.713867,2696.043945,2695.048584,2695.245117,2694.537354,2693.772949,2694.373779,2694.301514,2692.561523,2692.909180,2692.833252,2695.662598,2693.078857,2693.304932,2693.472168,2694.812012,2694.375000</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2684.771240,2685.439941,2683.952148,2684.794189,2682.207764,2682.171387,2680.888916,2676.944336,2675.039062,2672.891113,2671.010742,2669.886230,2666.814453,2666.659668,2665.751953,2664.607178,2663.592041,2663.631348,2660.343262,2659.546387,2659.889648,2658.957520,2658.971680,2658.746826</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2688.851562,2688.502197,2687.954590,2688.206055,2686.797119,2686.264648,2686.381348,2684.259033,2684.684814,2681.843750,2679.969727,2679.377441,2679.175293,2676.877441,2677.513672,2677.703125,2676.598633,2675.625000,2675.390137,2675.096436,2674.775391,2673.623047,2673.576660,2673.642334</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>2695.66845703125</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2699.550048828125</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3.881591796875</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.1437866209800407</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4421146184958973</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:04</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2694.575439453125</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>2693.331543,2693.802002,2694.307861,2695.177490,2695.184570,2695.820312,2696.276367,2695.466309,2695.259033,2695.124023,2695.357910,2695.401611,2694.703613,2694.080078,2694.515381,2694.543945,2694.521484,2694.520020,2694.931885,2694.630371,2695.035400,2695.466797,2695.491455,2695.668457</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2695.679932,2706.010010,2699.969971,2701.290039,2700.919922,2699.860107,2694.860107,2698.959961,2697.439941,2698.530029,2702.979980,2701.709961,2700.520020,2701.129883,2705.500000,2701.840088,2730.310059,2726.669922,2728.810059,2723.919922,2730.639893,2715.209961,2701.870117,2699.550049</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2.348389,12.208008,5.662110,6.112549,5.735352,4.039795,1.416260,3.493652,2.180908,3.406006,7.622070,6.308350,5.816407,7.049805,10.984619,7.296143,35.788575,32.149902,33.878174,29.289551,35.604493,19.743164,6.378662,3.881592</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.087117,0.451144,0.209710,0.226283,0.212348,0.149630,0.052554,0.129444,0.080851,0.126217,0.281988,0.233495,0.215381,0.260995,0.406011,0.270043,1.310788,1.179090,1.241500,1.075272,1.303888,0.727132,0.236083,0.143787</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4421146184958973</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>2692.884521,2695.052734,2694.552002,2694.608398,2695.383057,2696.531250,2696.734619,2695.713867,2696.043945,2695.048584,2695.245117,2694.537354,2693.772949,2694.373779,2694.301514,2692.561523,2692.909180,2692.833252,2695.662598,2693.078857,2693.304932,2693.472168,2694.812012,2694.375000</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>2688.851562,2688.502197,2687.954590,2688.206055,2686.797119,2686.264648,2686.381348,2684.259033,2684.684814,2681.843750,2679.969727,2679.377441,2679.175293,2676.877441,2677.513672,2677.703125,2676.598633,2675.625000,2675.390137,2675.096436,2674.775391,2673.623047,2673.576660,2673.642334</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:04</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2698.487793,2697.551270,2696.809082,2697.586182,2695.955811,2696.589355,2696.691895,2696.331787,2695.934326,2696.218018,2695.192627,2696.152344,2695.140869,2694.797363,2695.215820,2696.087402,2696.003418,2695.325684,2695.842773,2696.064697,2696.283691,2695.848877,2694.749023,2694.575439</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2696.889648,2698.608154,2696.132324,2697.484131,2696.961670,2695.767822,2695.596680,2695.617676,2694.366943,2696.529297,2694.381348,2692.236816,2692.750732,2694.928711,2693.732178,2693.649902,2692.632080,2692.332031,2694.128418,2692.505859,2692.624268,2694.264160,2692.964355,2692.059082</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2683.938965,2681.558838,2678.285645,2678.080322,2673.596436,2672.860840,2672.166016,2670.489746,2667.857178,2665.970703,2663.591797,2663.845703,2660.466553,2661.068848,2659.845703,2659.743164,2659.276123,2658.358887,2655.528809,2654.594482,2654.683105,2654.320312,2653.140625,2652.750732</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2690.696777,2687.451660,2685.377441,2684.933838,2682.091797,2681.116455,2681.124268,2680.030762,2679.982666,2678.101562,2674.835205,2675.565918,2674.512451,2673.484619,2674.133301,2674.818848,2674.649902,2673.337158,2672.799316,2672.689453,2672.343750,2671.291748,2670.106445,2670.380371</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>2694.575439453125</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2698.590087890625</v>
+      </c>
+      <c r="H79" t="n">
+        <v>4.0146484375</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.148768368175475</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.5369513824638235</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:13</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2697.72119140625</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>2698.487793,2697.551270,2696.809082,2697.586182,2695.955811,2696.589355,2696.691895,2696.331787,2695.934326,2696.218018,2695.192627,2696.152344,2695.140869,2694.797363,2695.215820,2696.087402,2696.003418,2695.325684,2695.842773,2696.064697,2696.283691,2695.848877,2694.749023,2694.575439</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2725.010010,2725.419922,2720.580078,2716.919922,2716.929932,2717.760010,2710.409912,2722.260010,2703.669922,2696.770020,2695.979980,2705.199951,2710.199951,2708.419922,2711.840088,2717.610107,2715.580078,2709.560059,2718.270020,2707.060059,2701.439941,2698.219971,2701.699951,2698.590088</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>26.522217,27.868652,23.770996,19.333740,20.974121,21.170655,13.718017,25.928223,7.735596,0.552002,0.787353,9.047607,15.059082,13.622559,16.624268,21.522705,19.576660,14.234375,22.427247,10.995362,5.156250,2.371094,6.950928,4.014649</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.973289,1.022545,0.873747,0.711605,0.771979,0.778974,0.506123,0.952452,0.286115,0.020469,0.029205,0.334452,0.555645,0.502971,0.613025,0.791972,0.720902,0.525339,0.825056,0.406174,0.190870,0.087876,0.257280,0.148768</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.5369513824638235</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>2696.889648,2698.608154,2696.132324,2697.484131,2696.961670,2695.767822,2695.596680,2695.617676,2694.366943,2696.529297,2694.381348,2692.236816,2692.750732,2694.928711,2693.732178,2693.649902,2692.632080,2692.332031,2694.128418,2692.505859,2692.624268,2694.264160,2692.964355,2692.059082</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>2690.696777,2687.451660,2685.377441,2684.933838,2682.091797,2681.116455,2681.124268,2680.030762,2679.982666,2678.101562,2674.835205,2675.565918,2674.512451,2673.484619,2674.133301,2674.818848,2674.649902,2673.337158,2672.799316,2672.689453,2672.343750,2671.291748,2670.106445,2670.380371</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:13</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2695.907227,2695.762939,2695.519043,2696.899658,2696.326172,2697.346680,2696.836426,2697.116211,2696.107666,2696.876953,2695.526367,2696.043701,2695.754883,2696.025635,2696.368652,2697.454346,2697.492676,2697.625000,2697.257568,2698.072754,2698.273926,2697.786377,2697.248047,2697.721191</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2694.919189,2696.811035,2695.735352,2697.753174,2698.405273,2696.910400,2697.026367,2696.444824,2695.853027,2695.026123,2696.292236,2693.910156,2693.074219,2696.334961,2694.474854,2694.644287,2695.079102,2695.626465,2696.815674,2693.723389,2695.014893,2696.383301,2695.863281,2694.269043</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2685.091553,2683.540039,2680.632080,2681.022949,2678.758545,2677.628662,2676.345703,2674.845703,2672.347656,2671.176270,2668.200439,2667.475830,2664.952637,2665.651611,2663.902344,2663.958252,2662.968018,2663.065674,2659.141602,2659.491699,2659.303223,2659.355225,2658.642822,2657.906250</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2690.359863,2688.257568,2686.449463,2687.116943,2684.937500,2684.792969,2683.948486,2683.993164,2682.585693,2681.871582,2678.089355,2678.875000,2678.071533,2677.583496,2677.697021,2678.592285,2677.545898,2677.508057,2676.615723,2677.354492,2677.283203,2675.583008,2675.111816,2675.562744</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>2697.72119140625</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2616.159912109375</v>
+      </c>
+      <c r="H80" t="n">
+        <v>81.561279296875</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3.11759533197316</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.997647436696022</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2628.2548828125</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>2695.907227,2695.762939,2695.519043,2696.899658,2696.326172,2697.346680,2696.836426,2697.116211,2696.107666,2696.876953,2695.526367,2696.043701,2695.754883,2696.025635,2696.368652,2697.454346,2697.492676,2697.625000,2697.257568,2698.072754,2698.273926,2697.786377,2697.248047,2697.721191</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2706.800049,2715.870117,2709.760010,2713.090088,2713.620117,2715.290039,2714.449951,2722.409912,2702.399902,2695.360107,2699.189941,2690.000000,2691.739990,2698.270020,2698.159912,2696.260010,2697.280029,2696.389893,2657.310059,2611.770020,2610.530029,2609.830078,2616.159912,2616.159912</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>10.892822,20.107178,14.240967,16.190430,17.293945,17.943359,17.613525,25.293701,6.292236,1.516846,3.663574,6.043701,4.014893,2.244385,1.791260,1.194336,0.212647,1.235107,39.947509,86.302734,87.743897,87.956299,81.088135,81.561279</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.402424,0.740359,0.525543,0.596752,0.637302,0.660827,0.648880,0.929092,0.232839,0.056276,0.135729,0.224673,0.149156,0.083179,0.066388,0.044296,0.007884,0.045806,1.503306,3.304377,3.361153,3.370193,3.099510,3.117595</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.997647436696022</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>2694.919189,2696.811035,2695.735352,2697.753174,2698.405273,2696.910400,2697.026367,2696.444824,2695.853027,2695.026123,2696.292236,2693.910156,2693.074219,2696.334961,2694.474854,2694.644287,2695.079102,2695.626465,2696.815674,2693.723389,2695.014893,2696.383301,2695.863281,2694.269043</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>2690.359863,2688.257568,2686.449463,2687.116943,2684.937500,2684.792969,2683.948486,2683.993164,2682.585693,2681.871582,2678.089355,2678.875000,2678.071533,2677.583496,2677.697021,2678.592285,2677.545898,2677.508057,2676.615723,2677.354492,2677.283203,2675.583008,2675.111816,2675.562744</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2617.089600,2617.208008,2617.938232,2618.385986,2618.940918,2619.357910,2619.636230,2619.419434,2619.040283,2620.466797,2620.170898,2621.380371,2622.186279,2622.733887,2623.476074,2624.039795,2626.060791,2626.731934,2627.498535,2627.738525,2628.251709,2628.760254,2627.903809,2628.254883</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2617.136230,2620.775391,2618.227539,2620.931396,2621.350342,2621.912109,2622.283691,2621.684326,2621.837646,2623.178223,2622.585938,2625.398438,2624.790527,2624.971191,2625.045654,2623.646484,2626.765869,2627.399414,2627.806641,2627.699463,2628.541260,2624.753418,2626.825439,2626.959961</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2597.923096,2593.661621,2589.735840,2586.656494,2583.140625,2579.538818,2579.395996,2576.463379,2573.434082,2571.209473,2568.625000,2568.729004,2566.486816,2567.313477,2565.910889,2563.636963,2565.313232,2564.069336,2559.521484,2557.701660,2557.407471,2557.193115,2556.331543,2554.741943</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2607.055664,2602.736084,2600.153076,2598.522705,2596.716797,2594.648193,2593.400635,2592.352783,2591.566650,2590.633301,2587.910645,2588.915771,2588.470947,2588.798828,2589.161621,2587.926758,2589.497559,2588.493896,2588.468262,2588.487305,2588.028076,2587.131836,2586.052979,2586.666260</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>2628.2548828125</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2567.9599609375</v>
+      </c>
+      <c r="H81" t="n">
+        <v>60.294921875</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.347969703273247</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.828582143923823</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:41</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2568.56103515625</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>2617.089600,2617.208008,2617.938232,2618.385986,2618.940918,2619.357910,2619.636230,2619.419434,2619.040283,2620.466797,2620.170898,2621.380371,2622.186279,2622.733887,2623.476074,2624.039795,2626.060791,2626.731934,2627.498535,2627.738525,2628.251709,2628.760254,2627.903809,2628.254883</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2617.489990,2615.810059,2608.969971,2596.250000,2579.090088,2577.379883,2571.989990,2568.459961,2562.459961,2569.399902,2567.189941,2549.919922,2561.199951,2569.550049,2572.760010,2566.260010,2568.229980,2572.800049,2574.520020,2576.449951,2578.590088,2562.520020,2560.820068,2567.959961</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.400390,1.397949,8.968261,22.135986,39.850830,41.978027,47.646240,50.959473,56.580322,51.066895,52.980957,71.460449,60.986328,53.183838,50.716064,57.779785,57.830811,53.931885,52.978515,51.288574,49.661621,66.240234,67.083741,60.294922</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.015297,0.053442,0.343747,0.852614,1.545151,1.628709,1.852505,1.984048,2.208047,1.987503,2.063772,2.802459,2.381162,2.069772,1.971271,2.251517,2.251777,2.096233,2.057802,1.990668,1.925922,2.584965,2.619619,2.347970</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1.828582143923823</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>2617.136230,2620.775391,2618.227539,2620.931396,2621.350342,2621.912109,2622.283691,2621.684326,2621.837646,2623.178223,2622.585938,2625.398438,2624.790527,2624.971191,2625.045654,2623.646484,2626.765869,2627.399414,2627.806641,2627.699463,2628.541260,2624.753418,2626.825439,2626.959961</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>2607.055664,2602.736084,2600.153076,2598.522705,2596.716797,2594.648193,2593.400635,2592.352783,2591.566650,2590.633301,2587.910645,2588.915771,2588.470947,2588.798828,2589.161621,2587.926758,2589.497559,2588.493896,2588.468262,2588.487305,2588.028076,2587.131836,2586.052979,2586.666260</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:41</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2566.834473,2567.172119,2567.585449,2568.172852,2568.093262,2568.404785,2568.216797,2567.381348,2566.029541,2567.489258,2566.684570,2568.387451,2567.439941,2569.262695,2570.334473,2570.247559,2568.647949,2570.281250,2570.873779,2570.948486,2570.935547,2570.103027,2568.902344,2568.561035</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2568.785645,2571.344727,2566.917969,2569.515137,2571.274170,2571.917969,2573.515137,2567.282471,2569.529785,2570.963867,2571.288330,2572.632812,2574.346191,2573.892090,2575.801270,2572.299561,2573.146973,2577.131836,2576.518311,2573.903564,2575.156738,2572.062012,2574.552490,2573.082520</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2555.871826,2552.137207,2547.770264,2545.787109,2542.184326,2540.130371,2541.116943,2538.150879,2533.722656,2532.089600,2529.664307,2531.739502,2528.234131,2528.706543,2528.675293,2526.566406,2524.183838,2523.705811,2518.380859,2517.414551,2516.239746,2515.280273,2514.655273,2513.660645</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2561.277588,2557.936523,2554.568848,2552.971924,2551.421631,2550.947266,2549.698975,2547.362549,2547.164062,2545.788818,2542.539062,2545.175781,2542.751953,2543.618408,2545.403320,2543.849121,2540.640869,2539.099609,2540.045410,2540.205566,2538.699707,2535.835205,2536.508057,2536.040039</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>2568.56103515625</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2488.419921875</v>
+      </c>
+      <c r="H82" t="n">
+        <v>80.14111328125</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3.220562276356655</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2.953564363007459</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:43</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2493.8681640625</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>2566.834473,2567.172119,2567.585449,2568.172852,2568.093262,2568.404785,2568.216797,2567.381348,2566.029541,2567.489258,2566.684570,2568.387451,2567.439941,2569.262695,2570.334473,2570.247559,2568.647949,2570.281250,2570.873779,2570.948486,2570.935547,2570.103027,2568.902344,2568.561035</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2564.959961,2566.560059,2558.090088,2565.919922,2549.300049,2535.379883,2527.860107,2520.340088,2529.979980,2433.350098,2414.550049,2415.790039,2445.810059,2462.840088,2473.770020,2477.229980,2474.389893,2472.889893,2476.370117,2480.530029,2487.459961,2491.310059,2485.120117,2488.419922</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1.874512,0.612060,9.495361,2.252930,18.793213,33.024902,40.356690,47.041260,36.049561,134.139160,152.134521,152.597412,121.629882,106.422607,96.564453,93.017579,94.258056,97.391357,94.503662,90.418457,83.475586,78.792968,83.782227,80.141113</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.073082,0.023847,0.371189,0.087802,0.737191,1.302562,1.596476,1.866465,1.424895,5.512530,6.300740,6.316667,4.972990,4.321133,3.903534,3.754903,3.809345,3.938362,3.816217,3.645126,3.355856,3.162712,3.371355,3.220562</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>2.953564363007459</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>2568.785645,2571.344727,2566.917969,2569.515137,2571.274170,2571.917969,2573.515137,2567.282471,2569.529785,2570.963867,2571.288330,2572.632812,2574.346191,2573.892090,2575.801270,2572.299561,2573.146973,2577.131836,2576.518311,2573.903564,2575.156738,2572.062012,2574.552490,2573.082520</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>2561.277588,2557.936523,2554.568848,2552.971924,2551.421631,2550.947266,2549.698975,2547.362549,2547.164062,2545.788818,2542.539062,2545.175781,2542.751953,2543.618408,2545.403320,2543.849121,2540.640869,2539.099609,2540.045410,2540.205566,2538.699707,2535.835205,2536.508057,2536.040039</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:43</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2488.795410,2489.499268,2488.468750,2488.235596,2487.944580,2488.528320,2488.713379,2488.153809,2487.277832,2488.933105,2486.114746,2487.680176,2488.206543,2490.331787,2489.440674,2490.184326,2489.666504,2491.511230,2492.556885,2493.619141,2493.794922,2494.044922,2492.728027,2493.868164</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2493.071777,2491.217773,2486.702881,2489.029541,2489.110352,2490.413574,2492.632080,2486.484375,2490.279541,2489.853027,2488.578125,2489.520996,2497.306152,2493.653076,2494.206543,2491.771484,2496.257324,2499.568604,2498.301270,2496.494141,2496.952637,2495.143799,2497.730957,2497.596436</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2470.999512,2467.298340,2461.059082,2457.316406,2454.188965,2452.273682,2453.472168,2451.915039,2448.448486,2447.257568,2442.077148,2441.792725,2438.722900,2438.453613,2435.887451,2434.323975,2433.124512,2431.832031,2427.540039,2425.891113,2425.491455,2425.204834,2424.363037,2424.538574</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2479.046875,2476.428955,2471.916016,2468.934326,2467.233398,2467.487305,2467.457275,2465.639160,2465.733643,2464.690430,2458.795898,2461.569092,2458.720703,2458.604736,2459.710693,2458.733643,2456.164551,2455.191895,2455.908691,2456.176025,2454.025635,2453.739746,2453.390869,2454.823730</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>2493.8681640625</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2495</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.1318359375</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.04536416583166333</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.2520364020021397</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:05</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2494.423583984375</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>2488.795410,2489.499268,2488.468750,2488.235596,2487.944580,2488.528320,2488.713379,2488.153809,2487.277832,2488.933105,2486.114746,2487.680176,2488.206543,2490.331787,2489.440674,2490.184326,2489.666504,2491.511230,2492.556885,2493.619141,2493.794922,2494.044922,2492.728027,2493.868164</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2497.389893,2502.540039,2503.169922,2500.110107,2490.560059,2504.219971,2495.800049,2482.699951,2488.810059,2487.000000,2489.439941,2485.699951,2481.129883,2474.379883,2480.719971,2482.879883,2486.889893,2485.229980,2487.100098,2493.360107,2490.860107,2489.139893,2492.639893,2495.000000</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>8.594483,13.040771,14.701172,11.874511,2.615479,15.691651,7.086670,5.453858,1.532227,1.933105,3.325195,1.980225,7.076660,15.951904,8.720703,7.304443,2.776611,6.281250,5.456787,0.259034,2.934815,4.905029,0.088134,1.131836</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.344139,0.521101,0.587302,0.474960,0.105016,0.626608,0.283944,0.219674,0.061565,0.077728,0.133572,0.079665,0.285219,0.644683,0.351539,0.294192,0.111650,0.252743,0.219404,0.010389,0.117823,0.197057,0.003536,0.045364</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.2520364020021397</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>2493.071777,2491.217773,2486.702881,2489.029541,2489.110352,2490.413574,2492.632080,2486.484375,2490.279541,2489.853027,2488.578125,2489.520996,2497.306152,2493.653076,2494.206543,2491.771484,2496.257324,2499.568604,2498.301270,2496.494141,2496.952637,2495.143799,2497.730957,2497.596436</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>2479.046875,2476.428955,2471.916016,2468.934326,2467.233398,2467.487305,2467.457275,2465.639160,2465.733643,2464.690430,2458.795898,2461.569092,2458.720703,2458.604736,2459.710693,2458.733643,2456.164551,2455.191895,2455.908691,2456.176025,2454.025635,2453.739746,2453.390869,2454.823730</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:05</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2495.753662,2495.232422,2495.403809,2494.673096,2494.938477,2494.915771,2495.025879,2494.425781,2493.259277,2493.766113,2492.389648,2492.728516,2493.340820,2493.402588,2493.186768,2493.615723,2492.284668,2494.270264,2494.007812,2494.385010,2494.468018,2494.902832,2493.693115,2494.423584</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2496.415039,2497.181885,2493.083984,2494.557129,2495.537598,2496.265137,2496.437256,2493.116943,2496.268555,2494.548340,2493.081299,2495.539795,2499.194092,2495.451660,2497.463379,2492.613281,2496.875488,2500.345215,2500.109863,2496.642822,2496.835938,2496.450439,2496.562744,2496.751465</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2482.790527,2478.388916,2473.218750,2469.770508,2467.016602,2465.574219,2465.537842,2462.775635,2458.771729,2457.346680,2453.636230,2452.732910,2450.332520,2448.668945,2447.043945,2443.506348,2442.303223,2441.648438,2436.692871,2435.277344,2434.075439,2434.671387,2433.894531,2432.056152</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2488.206787,2484.376221,2480.931641,2478.331543,2477.733154,2476.958252,2476.783203,2474.253418,2473.327637,2471.795898,2468.167236,2468.785889,2467.654785,2465.928467,2466.208740,2463.679199,2461.965088,2461.403809,2460.704346,2460.572266,2458.360352,2458.548828,2457.885986,2458.563477</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>2494.423583984375</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2506.090087890625</v>
+      </c>
+      <c r="H84" t="n">
+        <v>11.66650390625</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.4655261182597666</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3513047689176698</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:16</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2510.518310546875</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>2495.753662,2495.232422,2495.403809,2494.673096,2494.938477,2494.915771,2495.025879,2494.425781,2493.259277,2493.766113,2492.389648,2492.728516,2493.340820,2493.402588,2493.186768,2493.615723,2492.284668,2494.270264,2494.007812,2494.385010,2494.468018,2494.902832,2493.693115,2494.423584</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2491.139893,2492.919922,2493.659912,2494.550049,2493.669922,2494.899902,2494.129883,2497.149902,2506.010010,2509.419922,2503.050049,2505.719971,2509.580078,2510.860107,2506.010010,2507.580078,2507.669922,2503.860107,2501.739990,2508.179932,2508.260010,2497.000000,2504.689941,2506.090088</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>4.613769,2.312500,1.743897,0.123047,1.268555,0.015869,0.895996,2.724121,12.750733,15.653809,10.660401,12.991455,16.239258,17.457519,12.823242,13.964355,15.385254,9.589843,7.732178,13.794922,13.791992,2.097168,10.996826,11.666504</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.185207,0.092763,0.069933,0.004933,0.050871,0.000636,0.035924,0.109089,0.508806,0.623802,0.425896,0.518472,0.647091,0.695280,0.511700,0.556886,0.613528,0.383002,0.309072,0.549997,0.549863,0.083988,0.439049,0.465526</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3513047689176698</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>2496.415039,2497.181885,2493.083984,2494.557129,2495.537598,2496.265137,2496.437256,2493.116943,2496.268555,2494.548340,2493.081299,2495.539795,2499.194092,2495.451660,2497.463379,2492.613281,2496.875488,2500.345215,2500.109863,2496.642822,2496.835938,2496.450439,2496.562744,2496.751465</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>2488.206787,2484.376221,2480.931641,2478.331543,2477.733154,2476.958252,2476.783203,2474.253418,2473.327637,2471.795898,2468.167236,2468.785889,2467.654785,2465.928467,2466.208740,2463.679199,2461.965088,2461.403809,2460.704346,2460.572266,2458.360352,2458.548828,2457.885986,2458.563477</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:16</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2506.318359,2507.305664,2506.645996,2506.987793,2507.500000,2508.012695,2508.686523,2507.995361,2507.102051,2508.093018,2508.796143,2507.492188,2508.172607,2508.349365,2508.127441,2508.036133,2507.455811,2508.059082,2508.190186,2508.469971,2508.479492,2510.143799,2510.014893,2510.518311</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2508.606934,2507.515625,2506.646240,2506.741699,2506.474609,2509.604736,2509.316406,2508.939209,2507.747314,2507.442139,2510.396240,2509.093262,2509.752930,2508.600586,2509.565430,2505.780762,2510.418945,2511.939453,2511.059814,2510.771240,2512.557617,2511.941406,2511.458740,2511.327148</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2496.246338,2493.817383,2490.479004,2489.354980,2486.125977,2485.449219,2485.792725,2482.622070,2479.432129,2479.336182,2477.901367,2475.336182,2473.870117,2473.085449,2470.930908,2467.727051,2466.059326,2465.109619,2461.589844,2460.700195,2460.162109,2459.735596,2460.057129,2459.174805</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2501.235840,2499.399414,2497.391113,2496.250488,2495.468262,2495.038574,2495.140625,2493.227295,2492.610596,2491.500244,2491.641846,2489.471436,2489.274414,2487.760498,2488.022217,2485.183105,2485.017090,2483.706787,2483.334961,2482.946045,2481.838135,2482.320801,2481.443115,2481.913330</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>2510.518310546875</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2553.449951171875</v>
+      </c>
+      <c r="H85" t="n">
+        <v>42.931640625</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.681319056412171</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.8631781322769122</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2567.44140625</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>2506.318359,2507.305664,2506.645996,2506.987793,2507.500000,2508.012695,2508.686523,2507.995361,2507.102051,2508.093018,2508.796143,2507.492188,2508.172607,2508.349365,2508.127441,2508.036133,2507.455811,2508.059082,2508.190186,2508.469971,2508.479492,2510.143799,2510.014893,2510.518311</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2503.610107,2498.409912,2498.459961,2500.199951,2498.330078,2503.639893,2502.489990,2500.080078,2505.419922,2532.989990,2547.949951,2536.070068,2532.520020,2533.909912,2535.149902,2527.030029,2530.719971,2534.219971,2543.399902,2539.179932,2544.729980,2543.050049,2563.870117,2553.449951</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2.708252,8.895752,8.186035,6.787842,9.169922,4.372802,6.196533,7.915283,1.682129,24.896972,39.153808,28.577880,24.347413,25.560547,27.022461,18.993896,23.264160,26.160889,35.209716,30.709961,36.250488,32.906250,53.855224,42.931640</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.108174,0.356057,0.327643,0.271492,0.367042,0.174658,0.247615,0.316601,0.067140,0.982908,1.536679,1.126857,0.961391,1.008739,1.065912,0.751629,0.919270,1.032305,1.384356,1.209444,1.424532,1.293968,2.100544,1.681319</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.8631781322769122</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>2508.606934,2507.515625,2506.646240,2506.741699,2506.474609,2509.604736,2509.316406,2508.939209,2507.747314,2507.442139,2510.396240,2509.093262,2509.752930,2508.600586,2509.565430,2505.780762,2510.418945,2511.939453,2511.059814,2510.771240,2512.557617,2511.941406,2511.458740,2511.327148</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>2501.235840,2499.399414,2497.391113,2496.250488,2495.468262,2495.038574,2495.140625,2493.227295,2492.610596,2491.500244,2491.641846,2489.471436,2489.274414,2487.760498,2488.022217,2485.183105,2485.017090,2483.706787,2483.334961,2482.946045,2481.838135,2482.320801,2481.443115,2481.913330</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2551.473877,2552.720703,2553.415039,2554.297119,2555.214111,2555.965332,2557.385010,2557.172119,2557.981445,2559.399902,2560.534668,2560.486328,2562.064941,2562.090576,2562.230957,2563.288330,2563.605469,2563.890869,2564.481445,2564.762695,2565.625000,2566.074707,2566.931396,2567.441406</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2553.760254,2553.863281,2553.489014,2554.510742,2555.660645,2556.853760,2556.963379,2557.440186,2559.324951,2557.467529,2563.498535,2561.497559,2563.220459,2562.074219,2562.362793,2563.651855,2567.130615,2566.965088,2566.955322,2565.438965,2567.482666,2567.790283,2569.276611,2568.335938</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2536.741943,2533.758789,2531.712158,2530.796631,2527.443604,2526.741211,2526.214844,2524.006348,2522.289307,2522.113037,2521.222412,2520.175781,2519.008301,2518.644531,2515.826660,2515.446289,2514.025635,2513.123779,2508.489990,2507.147949,2508.150391,2507.817871,2508.046875,2506.953613</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2543.576172,2541.562256,2540.034180,2540.000977,2538.436523,2538.246582,2538.061279,2537.019287,2537.543457,2537.639404,2537.474609,2537.114014,2537.129395,2536.177490,2534.987305,2534.403564,2535.111816,2533.146240,2532.142090,2532.072754,2531.978516,2531.977295,2531.496582,2532.328369</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>2567.44140625</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2528.659912109375</v>
+      </c>
+      <c r="H86" t="n">
+        <v>38.781494140625</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.533677737955437</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.968577237359568</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:40</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2551.4345703125</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>2551.473877,2552.720703,2553.415039,2554.297119,2555.214111,2555.965332,2557.385010,2557.172119,2557.981445,2559.399902,2560.534668,2560.486328,2562.064941,2562.090576,2562.230957,2563.288330,2563.605469,2563.890869,2564.481445,2564.762695,2565.625000,2566.074707,2566.931396,2567.441406</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2568.100098,2561.570068,2549.479980,2557.699951,2553.350098,2543.570068,2529.350098,2539.560059,2521.020020,2527.610107,2510.860107,2508.969971,2510.770020,2518.459961,2516.110107,2487.709961,2465.729980,2444.300049,2418.520020,2461.540039,2488.820068,2505.620117,2514.669922,2528.659912</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>16.626221,8.849365,3.935059,3.402832,1.864013,12.395264,28.034912,17.612060,36.961425,31.789795,49.674561,51.516357,51.294921,43.630615,46.120850,75.578369,97.875489,119.590820,145.961425,103.222656,76.804932,60.454590,52.261474,38.781494</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.647413,0.345466,0.154347,0.133043,0.073003,0.487318,1.108384,0.693508,1.466130,1.257702,1.978388,2.053287,2.042996,1.732432,1.833022,3.038070,3.969433,4.892641,6.035155,4.193418,3.085998,2.412760,2.078264,1.533678</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1.968577237359568</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>2553.760254,2553.863281,2553.489014,2554.510742,2555.660645,2556.853760,2556.963379,2557.440186,2559.324951,2557.467529,2563.498535,2561.497559,2563.220459,2562.074219,2562.362793,2563.651855,2567.130615,2566.965088,2566.955322,2565.438965,2567.482666,2567.790283,2569.276611,2568.335938</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>2543.576172,2541.562256,2540.034180,2540.000977,2538.436523,2538.246582,2538.061279,2537.019287,2537.543457,2537.639404,2537.474609,2537.114014,2537.129395,2536.177490,2534.987305,2534.403564,2535.111816,2533.146240,2532.142090,2532.072754,2531.978516,2531.977295,2531.496582,2532.328369</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:40</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2531.933105,2534.269043,2535.579590,2536.055664,2536.717529,2537.358398,2538.703613,2538.496094,2539.873291,2541.849365,2542.545410,2542.565918,2543.141602,2543.001709,2543.118164,2544.133789,2544.653320,2544.792480,2545.293457,2545.814209,2546.271484,2547.988770,2551.222412,2551.434570</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2533.680908,2534.485840,2535.848877,2536.361084,2534.294434,2537.548340,2539.696777,2536.869141,2540.110596,2541.183105,2541.688477,2542.375244,2545.684570,2542.846680,2543.160400,2540.990723,2545.271484,2547.172852,2545.801758,2547.585205,2546.957520,2546.965332,2551.137451,2554.613037</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2515.900879,2512.905762,2508.955322,2505.763916,2501.685303,2499.807129,2497.787109,2493.871826,2492.879639,2491.261719,2488.950684,2486.842773,2486.571289,2483.395996,2480.862061,2479.770752,2478.958496,2477.575684,2472.283691,2472.395264,2472.564941,2474.274414,2477.180664,2475.558105</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2522.335205,2521.278809,2518.545410,2517.367188,2514.884766,2513.724609,2512.733154,2510.040771,2510.727539,2510.145508,2508.684082,2508.507324,2507.166260,2505.601074,2504.249268,2503.727539,2503.827393,2501.747070,2501.432861,2501.903809,2501.882324,2502.596191,2505.488770,2505.554199</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>2551.4345703125</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2514.360107421875</v>
+      </c>
+      <c r="H87" t="n">
+        <v>37.074462890625</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1.474508873298968</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.348374717616004</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:18</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2523.149169921875</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>2531.933105,2534.269043,2535.579590,2536.055664,2536.717529,2537.358398,2538.703613,2538.496094,2539.873291,2541.849365,2542.545410,2542.565918,2543.141602,2543.001709,2543.118164,2544.133789,2544.653320,2544.792480,2545.293457,2545.814209,2546.271484,2547.988770,2551.222412,2551.434570</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2526.689941,2515.209961,2511.600098,2495.929932,2497.229980,2502.090088,2500.520020,2514.030029,2513.699951,2510.229980,2498.310059,2506.370117,2505.310059,2508.310059,2510.090088,2509.010010,2495.639893,2505.370117,2503.879883,2511.919922,2511.139893,2514.360107,2514.360107,2514.360107</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>5.243164,19.059082,23.979492,40.125732,39.487549,35.268310,38.183593,24.466065,26.173340,31.619385,44.235351,36.195801,37.831543,34.691650,33.028076,35.123779,49.013427,39.422363,41.413574,33.894287,35.131591,33.628663,36.862305,37.074463</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.207511,0.757753,0.954750,1.607647,1.581254,1.409554,1.527026,0.973181,1.041228,1.259621,1.770611,1.444152,1.510054,1.383069,1.315812,1.399906,1.963962,1.573515,1.653976,1.349338,1.399030,1.337464,1.466071,1.474509</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>1.348374717616004</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>2533.680908,2534.485840,2535.848877,2536.361084,2534.294434,2537.548340,2539.696777,2536.869141,2540.110596,2541.183105,2541.688477,2542.375244,2545.684570,2542.846680,2543.160400,2540.990723,2545.271484,2547.172852,2545.801758,2547.585205,2546.957520,2546.965332,2551.137451,2554.613037</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>2522.335205,2521.278809,2518.545410,2517.367188,2514.884766,2513.724609,2512.733154,2510.040771,2510.727539,2510.145508,2508.684082,2508.507324,2507.166260,2505.601074,2504.249268,2503.727539,2503.827393,2501.747070,2501.432861,2501.903809,2501.882324,2502.596191,2505.488770,2505.554199</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:18</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2513.553955,2514.885254,2515.680420,2515.603516,2516.224609,2516.248291,2516.372559,2516.089355,2516.520996,2516.786865,2517.413818,2517.560547,2518.329102,2517.773438,2518.553467,2519.177002,2519.070801,2520.149414,2520.188232,2521.028320,2521.376221,2521.850098,2522.745117,2523.149170</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2514.867676,2513.524414,2516.246094,2514.773438,2516.182861,2517.193359,2516.798096,2516.895752,2517.212891,2516.559326,2518.752930,2519.996094,2523.070312,2520.855225,2521.630859,2518.139160,2522.060547,2523.072266,2523.535156,2523.903320,2523.861572,2523.381592,2525.534668,2526.645020</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2499.113281,2496.860840,2494.466797,2492.741455,2489.611816,2488.549072,2486.794922,2484.205078,2482.309326,2479.716064,2478.195068,2477.974121,2476.533691,2474.748535,2473.190918,2471.667480,2471.118408,2471.023438,2466.673340,2467.328613,2467.912109,2468.040039,2468.604980,2466.330566</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2505.091797,2503.981934,2502.212402,2501.612061,2500.321289,2499.086426,2498.161621,2496.441406,2496.738281,2494.342773,2493.554688,2493.473633,2493.041748,2491.143555,2491.305908,2490.625977,2490.433350,2489.031738,2489.547607,2490.847656,2490.580566,2489.915039,2490.685303,2490.267822</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>2523.149169921875</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2364.25</v>
+      </c>
+      <c r="H88" t="n">
+        <v>158.899169921875</v>
+      </c>
+      <c r="I88" t="n">
+        <v>6.720912336761129</v>
+      </c>
+      <c r="J88" t="n">
+        <v>3.133135389969237</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:18:53</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2380.96533203125</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>2513.553955,2514.885254,2515.680420,2515.603516,2516.224609,2516.248291,2516.372559,2516.089355,2516.520996,2516.786865,2517.413818,2517.560547,2518.329102,2517.773438,2518.553467,2519.177002,2519.070801,2520.149414,2520.188232,2521.028320,2521.376221,2521.850098,2522.745117,2523.149170</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2500.879883,2502.389893,2508.600098,2503.649902,2494.550049,2504.719971,2502.020020,2473.989990,2450.489990,2431.560059,2427.149902,2445.959961,2428.770020,2428.889893,2427.929932,2414.040039,2417.199951,2415.679932,2418.550049,2415.929932,2410.239990,2377.000000,2357.110107,2364.250000</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>12.674072,12.495361,7.080322,11.953614,21.674560,11.528320,14.352539,42.099365,66.031006,85.226806,90.263916,71.600586,89.559082,88.883545,90.623535,105.136963,101.870850,104.469482,101.638183,105.098388,111.136231,144.850098,165.635010,158.899170</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.506785,0.499337,0.282242,0.477447,0.868877,0.460264,0.573638,1.701679,2.694604,3.505026,3.718926,2.927300,3.687425,3.659431,3.732543,4.355229,4.214416,4.324641,4.202443,4.350225,4.611003,6.093820,7.027037,6.720912</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>3.133135389969237</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>2514.867676,2513.524414,2516.246094,2514.773438,2516.182861,2517.193359,2516.798096,2516.895752,2517.212891,2516.559326,2518.752930,2519.996094,2523.070312,2520.855225,2521.630859,2518.139160,2522.060547,2523.072266,2523.535156,2523.903320,2523.861572,2523.381592,2525.534668,2526.645020</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>2505.091797,2503.981934,2502.212402,2501.612061,2500.321289,2499.086426,2498.161621,2496.441406,2496.738281,2494.342773,2493.554688,2493.473633,2493.041748,2491.143555,2491.305908,2490.625977,2490.433350,2489.031738,2489.547607,2490.847656,2490.580566,2489.915039,2490.685303,2490.267822</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:18:53</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2366.140137,2366.186035,2366.315430,2366.074707,2367.764893,2367.163330,2367.848633,2367.891846,2368.854004,2368.727051,2368.726562,2369.580811,2371.038574,2373.035156,2373.289062,2375.447998,2375.255615,2377.950928,2378.623291,2379.859131,2380.105469,2380.290283,2380.286133,2380.965332</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2368.777832,2369.358154,2366.647217,2370.129883,2374.565430,2371.245605,2374.156006,2370.069824,2375.885986,2375.051025,2373.551514,2377.654297,2380.949951,2382.271973,2381.710449,2383.593750,2385.683105,2388.453857,2389.271484,2391.860352,2390.750000,2386.060059,2393.667236,2394.993408</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2341.611328,2336.139160,2331.996338,2328.328125,2326.102539,2322.945068,2321.814453,2318.280762,2316.795166,2313.010010,2310.370605,2310.196289,2309.576660,2308.039551,2307.521240,2307.365967,2304.936523,2306.889160,2301.929199,2301.181396,2300.906982,2299.024902,2298.612061,2296.165527</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2350.511230,2347.457520,2344.598877,2342.382812,2342.559082,2339.710693,2338.960449,2336.909668,2336.794678,2333.377441,2330.709717,2333.893799,2332.106934,2330.936035,2333.023926,2333.081055,2331.013672,2332.085938,2332.823242,2332.753174,2331.002441,2329.743652,2328.988037,2329.066406</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>2380.96533203125</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2437.219970703125</v>
+      </c>
+      <c r="H89" t="n">
+        <v>56.254638671875</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.308147781000081</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.830623507505161</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:27</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2439.40625</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>2366.140137,2366.186035,2366.315430,2366.074707,2367.764893,2367.163330,2367.848633,2367.891846,2368.854004,2368.727051,2368.726562,2369.580811,2371.038574,2373.035156,2373.289062,2375.447998,2375.255615,2377.950928,2378.623291,2379.859131,2380.105469,2380.290283,2380.286133,2380.965332</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2346.520020,2355.159912,2376.860107,2371.070068,2372.500000,2365.070068,2360.139893,2347.070068,2337.739990,2394.590088,2438.139893,2431.959961,2443.820068,2448.909912,2450.570068,2451.510010,2459.159912,2453.129883,2438.689941,2438.340088,2430.149902,2436.169922,2436.810059,2437.219971</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>19.620117,11.026123,10.544677,4.995361,4.735107,2.093262,7.708740,20.821778,31.114014,25.863037,69.413331,62.379150,72.781494,75.874756,77.281006,76.062012,83.904297,75.178955,60.066650,58.480957,50.044433,55.879639,56.523926,56.254639</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.836137,0.468169,0.443639,0.210680,0.199583,0.088507,0.326622,0.887139,1.330944,1.080061,2.846979,2.564974,2.978185,3.098307,3.153593,3.102660,3.411909,3.064614,2.463070,2.398392,2.059315,2.293750,2.319587,2.308148</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>1.830623507505161</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>2368.777832,2369.358154,2366.647217,2370.129883,2374.565430,2371.245605,2374.156006,2370.069824,2375.885986,2375.051025,2373.551514,2377.654297,2380.949951,2382.271973,2381.710449,2383.593750,2385.683105,2388.453857,2389.271484,2391.860352,2390.750000,2386.060059,2393.667236,2394.993408</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>2350.511230,2347.457520,2344.598877,2342.382812,2342.559082,2339.710693,2338.960449,2336.909668,2336.794678,2333.377441,2330.709717,2333.893799,2332.106934,2330.936035,2333.023926,2333.081055,2331.013672,2332.085938,2332.823242,2332.753174,2331.002441,2329.743652,2328.988037,2329.066406</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:27</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2435.114014,2435.459961,2435.813965,2435.169678,2436.423096,2436.304443,2435.902100,2436.895264,2437.074219,2437.494141,2438.534424,2438.337158,2438.862305,2440.661133,2439.999268,2440.200195,2439.635498,2440.943115,2440.488770,2439.428467,2439.229004,2439.731445,2439.584229,2439.406250</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2437.617432,2434.699463,2435.870361,2435.867676,2436.584961,2437.753906,2436.695068,2440.132324,2439.622559,2440.563232,2440.703125,2442.123535,2443.533203,2444.688232,2444.598877,2445.723633,2443.864746,2444.352783,2442.331055,2443.498535,2442.720215,2443.447998,2443.296387,2444.890625</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2414.398926,2408.718750,2404.628662,2401.452148,2400.354004,2397.488281,2393.955566,2392.361572,2389.197510,2387.689941,2386.496094,2385.196533,2383.591797,2383.718262,2381.087646,2378.334717,2375.692871,2375.640625,2369.016602,2366.812988,2365.968750,2365.757080,2363.540039,2359.952393</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2422.929932,2418.739746,2415.784912,2414.713867,2414.867188,2412.967041,2410.577637,2409.410889,2409.265381,2407.487793,2405.960938,2407.316650,2404.576904,2405.324219,2405.077881,2403.764160,2400.254150,2399.068604,2398.740723,2396.890381,2395.764648,2394.005615,2393.627930,2392.306152</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>2439.40625</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2423.320068359375</v>
+      </c>
+      <c r="H90" t="n">
+        <v>16.086181640625</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.6638075527313894</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8544021234114861</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:34</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2427.614501953125</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>2435.114014,2435.459961,2435.813965,2435.169678,2436.423096,2436.304443,2435.902100,2436.895264,2437.074219,2437.494141,2438.534424,2438.337158,2438.862305,2440.661133,2439.999268,2440.200195,2439.635498,2440.943115,2440.488770,2439.428467,2439.229004,2439.731445,2439.584229,2439.406250</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2444.409912,2446.290039,2451.729980,2454.560059,2447.399902,2462.360107,2474.209961,2459.600098,2455.939941,2456.540039,2428.320068,2428.370117,2408.020020,2402.959961,2409.850098,2412.860107,2412.770020,2422.060059,2419.919922,2419.689941,2416.570068,2418.800049,2424.280029,2423.320068</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>9.295898,10.830078,15.916015,19.390381,10.976806,26.055664,38.307861,22.704834,18.865722,19.045898,10.214356,9.967041,30.842285,37.701172,30.149170,27.340088,26.865478,18.883056,20.568848,19.738526,22.658936,20.931396,15.304200,16.086182</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.380292,0.442714,0.649175,0.789974,0.448509,1.058158,1.548287,0.923111,0.768167,0.775314,0.420635,0.410442,1.280815,1.568947,1.251081,1.133099,1.113470,0.779628,0.849981,0.815746,0.937649,0.865363,0.631288,0.663808</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8544021234114861</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>2437.617432,2434.699463,2435.870361,2435.867676,2436.584961,2437.753906,2436.695068,2440.132324,2439.622559,2440.563232,2440.703125,2442.123535,2443.533203,2444.688232,2444.598877,2445.723633,2443.864746,2444.352783,2442.331055,2443.498535,2442.720215,2443.447998,2443.296387,2444.890625</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>2422.929932,2418.739746,2415.784912,2414.713867,2414.867188,2412.967041,2410.577637,2409.410889,2409.265381,2407.487793,2405.960938,2407.316650,2404.576904,2405.324219,2405.077881,2403.764160,2400.254150,2399.068604,2398.740723,2396.890381,2395.764648,2394.005615,2393.627930,2392.306152</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:34</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2422.122070,2423.674805,2424.694824,2424.363281,2425.139160,2424.308594,2424.033203,2424.688477,2424.464355,2424.641113,2424.533203,2423.392578,2423.479980,2424.510010,2423.882568,2424.729736,2424.462646,2425.158936,2424.761719,2425.028320,2425.838623,2426.353516,2426.862305,2427.614502</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2422.183105,2423.155518,2424.467773,2422.855225,2424.626953,2424.883789,2427.625000,2426.564941,2428.109131,2426.726318,2427.966309,2429.142578,2428.957520,2425.666016,2428.770508,2428.336914,2429.526855,2431.288574,2428.151123,2431.527832,2433.768066,2431.016846,2433.555664,2434.180420</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2405.272461,2403.092773,2401.284180,2398.927979,2397.438965,2394.834473,2393.187012,2390.696289,2389.152832,2386.883789,2384.755371,2383.193359,2382.161621,2381.486084,2379.295410,2377.810059,2376.003906,2375.986328,2370.924316,2370.641602,2370.563965,2370.915039,2370.131104,2367.122559</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2412.359619,2411.024902,2410.493408,2409.483643,2408.821289,2407.265137,2405.575684,2404.909424,2404.721924,2403.229980,2401.491699,2400.911621,2399.373047,2399.665527,2399.076172,2399.161377,2396.044189,2395.797852,2395.329102,2394.713135,2394.734375,2393.298828,2392.987549,2392.703613</t>
         </is>
       </c>
     </row>
